--- a/research/traditional_assets/database/data/brazil/brazil_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_software_entertainment.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,35 +587,32 @@
           <t>Software (Entertainment)</t>
         </is>
       </c>
-      <c r="F2">
-        <v>0.0592</v>
-      </c>
       <c r="G2">
-        <v>-0.05278918918918918</v>
+        <v>-0.4357954545454546</v>
       </c>
       <c r="H2">
-        <v>-0.2454054054054054</v>
+        <v>-0.5159090909090909</v>
       </c>
       <c r="I2">
-        <v>-0.5232432432432432</v>
+        <v>-0.4045454545454545</v>
       </c>
       <c r="J2">
-        <v>-0.5232432432432432</v>
+        <v>-0.4045454545454545</v>
       </c>
       <c r="K2">
-        <v>-22.31</v>
+        <v>-40.12</v>
       </c>
       <c r="L2">
-        <v>-0.2411891891891892</v>
+        <v>-0.3039393939393939</v>
       </c>
       <c r="M2">
-        <v>2.25</v>
+        <v>0.106</v>
       </c>
       <c r="N2">
-        <v>0.009920634920634922</v>
+        <v>0.000452604611443211</v>
       </c>
       <c r="O2">
-        <v>-0.1008516360376513</v>
+        <v>-0.002642073778664008</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,73 +624,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>2.25</v>
+        <v>0.106</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>126.8</v>
+        <v>102.2</v>
       </c>
       <c r="V2">
-        <v>0.5590828924162259</v>
+        <v>0.4363791631084544</v>
       </c>
       <c r="W2">
-        <v>0.8399944974321349</v>
+        <v>-0.1017421602787456</v>
       </c>
       <c r="X2">
-        <v>0.2356699388092812</v>
+        <v>0.161742893766567</v>
       </c>
       <c r="Y2">
-        <v>0.6043245586228538</v>
+        <v>-0.2634850540453126</v>
       </c>
       <c r="Z2">
-        <v>11.40848544647264</v>
+        <v>4.754529409645933</v>
+      </c>
+      <c r="AA2">
+        <v>-1.503315171010308</v>
       </c>
       <c r="AB2">
-        <v>0.1956499661398779</v>
+        <v>0.1603527223158827</v>
+      </c>
+      <c r="AC2">
+        <v>-1.663959797247951</v>
       </c>
       <c r="AD2">
-        <v>20.333</v>
+        <v>22.134</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>20.333</v>
+        <v>22.134</v>
       </c>
       <c r="AG2">
-        <v>-106.467</v>
+        <v>-80.066</v>
       </c>
       <c r="AH2">
-        <v>0.08227553584507129</v>
+        <v>0.0863482799784656</v>
       </c>
       <c r="AI2">
-        <v>0.1440697781525228</v>
+        <v>0.1072726744016982</v>
       </c>
       <c r="AJ2">
-        <v>-0.8847697639051635</v>
+        <v>-0.5194570957738073</v>
       </c>
       <c r="AK2">
-        <v>-7.428102979139052</v>
+        <v>-0.7688747191119134</v>
       </c>
       <c r="AL2">
-        <v>2.08</v>
+        <v>7.483000000000001</v>
       </c>
       <c r="AM2">
-        <v>-13.8</v>
+        <v>-19.197</v>
       </c>
       <c r="AN2">
-        <v>-0.4209730848861284</v>
+        <v>-0.3966666666666667</v>
       </c>
       <c r="AO2">
-        <v>-23.26923076923077</v>
+        <v>-7.136175330749698</v>
       </c>
       <c r="AP2">
-        <v>2.204285714285715</v>
+        <v>1.434874551971326</v>
       </c>
       <c r="AQ2">
-        <v>3.507246376811594</v>
+        <v>2.781684638224723</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Méliuz S.A. (BOVESPA:CASH3)</t>
+          <t>Enjoei S.A. (BOVESPA:ENJU3)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,35 +715,32 @@
           <t>Software (Entertainment)</t>
         </is>
       </c>
-      <c r="F3">
-        <v>0.0592</v>
-      </c>
       <c r="G3">
-        <v>-0.1449333333333333</v>
+        <v>-0.4381818181818182</v>
       </c>
       <c r="H3">
-        <v>-0.1496296296296296</v>
+        <v>-0.5424242424242424</v>
       </c>
       <c r="I3">
-        <v>-0.4444444444444444</v>
+        <v>-0.4212121212121212</v>
       </c>
       <c r="J3">
-        <v>-0.4444444444444444</v>
+        <v>-0.4212121212121212</v>
       </c>
       <c r="K3">
-        <v>-5.81</v>
+        <v>-8.82</v>
       </c>
       <c r="L3">
-        <v>-0.08607407407407407</v>
+        <v>-0.2672727272727273</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.005701078582434516</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.1910499139414802</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +752,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>1.11</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>89.90000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="V3">
-        <v>0.4617360041088855</v>
+        <v>0.7725988700564973</v>
       </c>
       <c r="W3">
-        <v>-0.04414893617021277</v>
+        <v>-0.1244005641748942</v>
       </c>
       <c r="X3">
-        <v>0.201689237106516</v>
+        <v>0.161742893766567</v>
       </c>
       <c r="Y3">
-        <v>-0.2458381732767288</v>
+        <v>-0.2861434579414612</v>
       </c>
       <c r="Z3">
-        <v>8.325111001480037</v>
+        <v>2.633679169992017</v>
       </c>
       <c r="AA3">
-        <v>-3.700049333991128</v>
+        <v>-1.109337589784516</v>
       </c>
       <c r="AB3">
-        <v>0.201665752349859</v>
+        <v>0.1603527223158827</v>
       </c>
       <c r="AC3">
-        <v>-3.901715086340987</v>
+        <v>-1.269690312100399</v>
       </c>
       <c r="AD3">
-        <v>0.033</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.033</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="AG3">
-        <v>-89.867</v>
+        <v>-53.764</v>
       </c>
       <c r="AH3">
-        <v>0.0001694628029147602</v>
+        <v>0.01304784208765473</v>
       </c>
       <c r="AI3">
-        <v>0.0002262862315113863</v>
+        <v>0.0130296787126232</v>
       </c>
       <c r="AJ3">
-        <v>-0.8572396096648958</v>
+        <v>-3.155905142052126</v>
       </c>
       <c r="AK3">
-        <v>-1.606690147140329</v>
+        <v>-3.137488328664799</v>
       </c>
       <c r="AL3">
-        <v>0.19</v>
+        <v>2.72</v>
       </c>
       <c r="AM3">
-        <v>-11.01</v>
+        <v>-4.959999999999999</v>
       </c>
       <c r="AN3">
-        <v>-0.00113013698630137</v>
+        <v>-0.0585</v>
       </c>
       <c r="AO3">
-        <v>-157.8947368421053</v>
+        <v>-5.110294117647059</v>
       </c>
       <c r="AP3">
-        <v>3.07763698630137</v>
+        <v>3.36025</v>
       </c>
       <c r="AQ3">
-        <v>2.724795640326976</v>
+        <v>2.80241935483871</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dotz S.A. (BOVESPA:DOTZ3)</t>
+          <t>Méliuz S.A. (BOVESPA:CASH3)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,31 +841,31 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.196</v>
+        <v>-0.4316713483146067</v>
       </c>
       <c r="H4">
-        <v>-0.504</v>
+        <v>-0.4438202247191012</v>
       </c>
       <c r="I4">
-        <v>-0.736</v>
+        <v>-0.321629213483146</v>
       </c>
       <c r="J4">
-        <v>-0.736</v>
+        <v>-0.321629213483146</v>
       </c>
       <c r="K4">
-        <v>-16.5</v>
+        <v>-14.6</v>
       </c>
       <c r="L4">
-        <v>-0.66</v>
+        <v>-0.2050561797752809</v>
       </c>
       <c r="M4">
-        <v>1.14</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.03551401869158878</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.06909090909090909</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -880,70 +877,195 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>1.14</v>
-      </c>
-      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>33.2</v>
+      </c>
+      <c r="V4">
+        <v>0.2334739803094234</v>
+      </c>
+      <c r="W4">
+        <v>-0.1017421602787456</v>
+      </c>
+      <c r="X4">
+        <v>0.1607914496402955</v>
+      </c>
+      <c r="Y4">
+        <v>-0.2625336099190412</v>
+      </c>
+      <c r="Z4">
+        <v>4.674062889778775</v>
+      </c>
+      <c r="AA4">
+        <v>-1.503315171010308</v>
+      </c>
+      <c r="AB4">
+        <v>0.1606446262376433</v>
+      </c>
+      <c r="AC4">
+        <v>-1.663959797247951</v>
+      </c>
+      <c r="AD4">
+        <v>0.198</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.198</v>
+      </c>
+      <c r="AG4">
+        <v>-33.002</v>
+      </c>
+      <c r="AH4">
+        <v>0.001390468967260776</v>
+      </c>
+      <c r="AI4">
+        <v>0.001253180420005316</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.3022216524112164</v>
+      </c>
+      <c r="AK4">
+        <v>-0.264443340438148</v>
+      </c>
+      <c r="AL4">
+        <v>0.143</v>
+      </c>
+      <c r="AM4">
+        <v>-15.157</v>
+      </c>
+      <c r="AN4">
+        <v>-0.00908256880733945</v>
+      </c>
+      <c r="AO4">
+        <v>-160.1398601398601</v>
+      </c>
+      <c r="AP4">
+        <v>1.513853211009174</v>
+      </c>
+      <c r="AQ4">
+        <v>1.51085307118823</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dotz S.A. (BOVESPA:DOTZ3)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Software (Entertainment)</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>-0.4435251798561152</v>
+      </c>
+      <c r="H5">
+        <v>-0.6690647482014389</v>
+      </c>
+      <c r="I5">
+        <v>-0.5971223021582734</v>
+      </c>
+      <c r="J5">
+        <v>-0.5971223021582734</v>
+      </c>
+      <c r="K5">
+        <v>-16.7</v>
+      </c>
+      <c r="L5">
+        <v>-0.6007194244604316</v>
+      </c>
+      <c r="M5">
+        <v>0.106</v>
+      </c>
+      <c r="N5">
+        <v>0.005</v>
+      </c>
+      <c r="O5">
+        <v>-0.006347305389221557</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0.106</v>
+      </c>
+      <c r="T5">
         <v>1</v>
       </c>
-      <c r="U4">
-        <v>36.9</v>
-      </c>
-      <c r="V4">
-        <v>1.149532710280374</v>
-      </c>
-      <c r="W4">
-        <v>1.724137931034483</v>
-      </c>
-      <c r="X4">
-        <v>0.2696506405120463</v>
-      </c>
-      <c r="Y4">
-        <v>1.454487290522436</v>
-      </c>
-      <c r="AB4">
-        <v>0.1896341799298969</v>
-      </c>
-      <c r="AD4">
-        <v>20.3</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>20.3</v>
-      </c>
-      <c r="AG4">
-        <v>-16.6</v>
-      </c>
-      <c r="AH4">
-        <v>0.3874045801526717</v>
-      </c>
-      <c r="AI4">
-        <v>-4.319148936170214</v>
-      </c>
-      <c r="AJ4">
-        <v>-1.070967741935483</v>
-      </c>
-      <c r="AK4">
-        <v>0.3990384615384616</v>
-      </c>
-      <c r="AL4">
-        <v>1.89</v>
-      </c>
-      <c r="AM4">
-        <v>-2.79</v>
-      </c>
-      <c r="AN4">
-        <v>-1.06282722513089</v>
-      </c>
-      <c r="AO4">
-        <v>-9.735449735449736</v>
-      </c>
-      <c r="AP4">
-        <v>0.8691099476439789</v>
-      </c>
-      <c r="AQ4">
-        <v>6.594982078853046</v>
+      <c r="U5">
+        <v>14.3</v>
+      </c>
+      <c r="V5">
+        <v>0.6745283018867925</v>
+      </c>
+      <c r="W5">
+        <v>0.6679999999999999</v>
+      </c>
+      <c r="X5">
+        <v>0.2403610049872916</v>
+      </c>
+      <c r="Y5">
+        <v>0.4276389950127083</v>
+      </c>
+      <c r="AB5">
+        <v>0.1482186396465618</v>
+      </c>
+      <c r="AD5">
+        <v>21</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>21</v>
+      </c>
+      <c r="AG5">
+        <v>6.699999999999999</v>
+      </c>
+      <c r="AH5">
+        <v>0.4976303317535545</v>
+      </c>
+      <c r="AI5">
+        <v>-0.8936170212765957</v>
+      </c>
+      <c r="AJ5">
+        <v>0.2401433691756272</v>
+      </c>
+      <c r="AK5">
+        <v>-0.1772486772486772</v>
+      </c>
+      <c r="AL5">
+        <v>4.62</v>
+      </c>
+      <c r="AM5">
+        <v>0.9199999999999999</v>
+      </c>
+      <c r="AN5">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AO5">
+        <v>-3.593073593073593</v>
+      </c>
+      <c r="AP5">
+        <v>-0.3722222222222222</v>
+      </c>
+      <c r="AQ5">
+        <v>-18.04347826086957</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/brazil/brazil_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_software_entertainment.xlsx
@@ -1391,7 +1391,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1528,22 +1528,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1496987986468103</v>
+        <v>0.1492195227314111</v>
       </c>
       <c r="C2">
-        <v>38.83611900997276</v>
+        <v>38.59857980410596</v>
       </c>
       <c r="D2">
-        <v>32.56611900997276</v>
+        <v>32.71703980410597</v>
       </c>
       <c r="E2">
-        <v>-0.046</v>
+        <v>0.34246</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.38846</v>
       </c>
       <c r="G2">
         <v>6.27</v>
@@ -1564,28 +1564,28 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.019539538</v>
       </c>
       <c r="N2">
-        <v>0.9300000000000002</v>
+        <v>0.9104604620000002</v>
       </c>
       <c r="O2">
-        <v>0.3162000000000001</v>
+        <v>0.3095565570800001</v>
       </c>
       <c r="P2">
-        <v>0.6138000000000001</v>
+        <v>0.6009039049200001</v>
       </c>
       <c r="Q2">
-        <v>2.5138</v>
+        <v>2.50090390492</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1496987986468103</v>
+        <v>0.1503914573044557</v>
       </c>
       <c r="T2">
-        <v>1.354149646462541</v>
+        <v>1.363177310772291</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>47.59580293044801</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1610,22 +1610,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1492195227314111</v>
+        <v>0.1487402468160119</v>
       </c>
       <c r="C3">
-        <v>38.59857980410596</v>
+        <v>38.36244593199346</v>
       </c>
       <c r="D3">
-        <v>32.71703980410597</v>
+        <v>32.86936593199345</v>
       </c>
       <c r="E3">
-        <v>0.34246</v>
+        <v>0.7309199999999999</v>
       </c>
       <c r="F3">
-        <v>0.38846</v>
+        <v>0.7769199999999999</v>
       </c>
       <c r="G3">
         <v>6.27</v>
@@ -1646,28 +1646,28 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M3">
-        <v>0.019539538</v>
+        <v>0.039079076</v>
       </c>
       <c r="N3">
-        <v>0.9104604620000002</v>
+        <v>0.8909209240000001</v>
       </c>
       <c r="O3">
-        <v>0.3095565570800001</v>
+        <v>0.3029131141600001</v>
       </c>
       <c r="P3">
-        <v>0.6009039049200001</v>
+        <v>0.5880078098400001</v>
       </c>
       <c r="Q3">
-        <v>2.50090390492</v>
+        <v>2.48800780984</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1503914573044557</v>
+        <v>0.1510982518530734</v>
       </c>
       <c r="T3">
-        <v>1.363177310772291</v>
+        <v>1.372389213129179</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>47.59580293044801</v>
+        <v>23.797901465224</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1692,22 +1692,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1487402468160119</v>
+        <v>0.1482609709006128</v>
       </c>
       <c r="C4">
-        <v>38.36244593199346</v>
+        <v>38.12773711458692</v>
       </c>
       <c r="D4">
-        <v>32.86936593199345</v>
+        <v>33.02311711458692</v>
       </c>
       <c r="E4">
-        <v>0.7309199999999999</v>
+        <v>1.11938</v>
       </c>
       <c r="F4">
-        <v>0.7769199999999999</v>
+        <v>1.16538</v>
       </c>
       <c r="G4">
         <v>6.27</v>
@@ -1728,28 +1728,28 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M4">
-        <v>0.039079076</v>
+        <v>0.05861861399999999</v>
       </c>
       <c r="N4">
-        <v>0.8909209240000001</v>
+        <v>0.8713813860000001</v>
       </c>
       <c r="O4">
-        <v>0.3029131141600001</v>
+        <v>0.2962696712400001</v>
       </c>
       <c r="P4">
-        <v>0.5880078098400001</v>
+        <v>0.57511171476</v>
       </c>
       <c r="Q4">
-        <v>2.48800780984</v>
+        <v>2.47511171476</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1510982518530734</v>
+        <v>0.1518196194851679</v>
       </c>
       <c r="T4">
-        <v>1.372389213129179</v>
+        <v>1.381791051617137</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1766,7 +1766,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>23.797901465224</v>
+        <v>15.86526764348267</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1774,22 +1774,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1482609709006128</v>
+        <v>0.1478212949852137</v>
       </c>
       <c r="C5">
-        <v>38.12773711458692</v>
+        <v>37.88159513994422</v>
       </c>
       <c r="D5">
-        <v>33.02311711458692</v>
+        <v>33.16543513994421</v>
       </c>
       <c r="E5">
-        <v>1.11938</v>
+        <v>1.50784</v>
       </c>
       <c r="F5">
-        <v>1.16538</v>
+        <v>1.55384</v>
       </c>
       <c r="G5">
         <v>6.27</v>
@@ -1810,45 +1810,45 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M5">
-        <v>0.05861861399999999</v>
+        <v>0.080488912</v>
       </c>
       <c r="N5">
-        <v>0.8713813860000001</v>
+        <v>0.8495110880000002</v>
       </c>
       <c r="O5">
-        <v>0.2962696712400001</v>
+        <v>0.2888337699200001</v>
       </c>
       <c r="P5">
-        <v>0.57511171476</v>
+        <v>0.5606773180800001</v>
       </c>
       <c r="Q5">
-        <v>2.47511171476</v>
+        <v>2.46067731808</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1518196194851679</v>
+        <v>0.1525560156095976</v>
       </c>
       <c r="T5">
-        <v>1.381791051617137</v>
+        <v>1.391388761740261</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V5">
         <v>0.34</v>
       </c>
       <c r="W5">
-        <v>0.03319799999999999</v>
+        <v>0.034188</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y5">
-        <v>15.86526764348267</v>
+        <v>11.55438652220818</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1856,22 +1856,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1478212949852137</v>
+        <v>0.1474080190698145</v>
       </c>
       <c r="C6">
-        <v>37.88159513994422</v>
+        <v>37.62803074850493</v>
       </c>
       <c r="D6">
-        <v>33.16543513994421</v>
+        <v>33.30033074850493</v>
       </c>
       <c r="E6">
-        <v>1.50784</v>
+        <v>1.8963</v>
       </c>
       <c r="F6">
-        <v>1.55384</v>
+        <v>1.9423</v>
       </c>
       <c r="G6">
         <v>6.27</v>
@@ -1892,45 +1892,45 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M6">
-        <v>0.080488912</v>
+        <v>0.10391305</v>
       </c>
       <c r="N6">
-        <v>0.8495110880000002</v>
+        <v>0.8260869500000002</v>
       </c>
       <c r="O6">
-        <v>0.2888337699200001</v>
+        <v>0.2808695630000001</v>
       </c>
       <c r="P6">
-        <v>0.5606773180800001</v>
+        <v>0.5452173870000001</v>
       </c>
       <c r="Q6">
-        <v>2.46067731808</v>
+        <v>2.445217387</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1525560156095976</v>
+        <v>0.1533079148103311</v>
       </c>
       <c r="T6">
-        <v>1.391388761740261</v>
+        <v>1.401188528918608</v>
       </c>
       <c r="U6">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V6">
         <v>0.34</v>
       </c>
       <c r="W6">
-        <v>0.034188</v>
+        <v>0.03530999999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>11.55438652220818</v>
+        <v>8.949790233276765</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1938,22 +1938,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1474080190698145</v>
+        <v>0.1469815431544154</v>
       </c>
       <c r="C7">
-        <v>37.62803074850493</v>
+        <v>37.37993023103813</v>
       </c>
       <c r="D7">
-        <v>33.30033074850493</v>
+        <v>33.44069023103813</v>
       </c>
       <c r="E7">
-        <v>1.8963</v>
+        <v>2.28476</v>
       </c>
       <c r="F7">
-        <v>1.9423</v>
+        <v>2.33076</v>
       </c>
       <c r="G7">
         <v>6.27</v>
@@ -1974,45 +1974,45 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M7">
-        <v>0.10391305</v>
+        <v>0.126560268</v>
       </c>
       <c r="N7">
-        <v>0.8260869500000002</v>
+        <v>0.8034397320000002</v>
       </c>
       <c r="O7">
-        <v>0.2808695630000001</v>
+        <v>0.2731695088800001</v>
       </c>
       <c r="P7">
-        <v>0.5452173870000001</v>
+        <v>0.5302702231200001</v>
       </c>
       <c r="Q7">
-        <v>2.445217387</v>
+        <v>2.43027022312</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1533079148103311</v>
+        <v>0.1540758118663993</v>
       </c>
       <c r="T7">
-        <v>1.401188528918608</v>
+        <v>1.411196801781601</v>
       </c>
       <c r="U7">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V7">
         <v>0.34</v>
       </c>
       <c r="W7">
-        <v>0.03530999999999999</v>
+        <v>0.03583799999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y7">
-        <v>8.949790233276765</v>
+        <v>7.348277739108455</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2020,22 +2020,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1469815431544154</v>
+        <v>0.1465286672390162</v>
       </c>
       <c r="C8">
-        <v>37.37993023103813</v>
+        <v>37.14181951704651</v>
       </c>
       <c r="D8">
-        <v>33.44069023103813</v>
+        <v>33.5910395170465</v>
       </c>
       <c r="E8">
-        <v>2.28476</v>
+        <v>2.67322</v>
       </c>
       <c r="F8">
-        <v>2.33076</v>
+        <v>2.71922</v>
       </c>
       <c r="G8">
         <v>6.27</v>
@@ -2056,28 +2056,28 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M8">
-        <v>0.126560268</v>
+        <v>0.147653646</v>
       </c>
       <c r="N8">
-        <v>0.8034397320000002</v>
+        <v>0.7823463540000002</v>
       </c>
       <c r="O8">
-        <v>0.2731695088800001</v>
+        <v>0.2659977603600001</v>
       </c>
       <c r="P8">
-        <v>0.5302702231200001</v>
+        <v>0.5163485936400001</v>
       </c>
       <c r="Q8">
-        <v>2.43027022312</v>
+        <v>2.41634859364</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1540758118663993</v>
+        <v>0.1548602228376518</v>
       </c>
       <c r="T8">
-        <v>1.411196801781601</v>
+        <v>1.421420306319067</v>
       </c>
       <c r="U8">
         <v>0.0543</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>7.348277739108457</v>
+        <v>6.298523776378677</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2102,22 +2102,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1465286672390162</v>
+        <v>0.1461285913236171</v>
       </c>
       <c r="C9">
-        <v>37.14181951704649</v>
+        <v>36.88730902941076</v>
       </c>
       <c r="D9">
-        <v>33.59103951704649</v>
+        <v>33.72498902941076</v>
       </c>
       <c r="E9">
-        <v>2.67322</v>
+        <v>3.06168</v>
       </c>
       <c r="F9">
-        <v>2.71922</v>
+        <v>3.10768</v>
       </c>
       <c r="G9">
         <v>6.27</v>
@@ -2138,45 +2138,45 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M9">
-        <v>0.147653646</v>
+        <v>0.171854704</v>
       </c>
       <c r="N9">
-        <v>0.7823463540000002</v>
+        <v>0.7581452960000001</v>
       </c>
       <c r="O9">
-        <v>0.2659977603600001</v>
+        <v>0.2577694006400001</v>
       </c>
       <c r="P9">
-        <v>0.5163485936400001</v>
+        <v>0.50037589536</v>
       </c>
       <c r="Q9">
-        <v>2.41634859364</v>
+        <v>2.40037589536</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1548602228376519</v>
+        <v>0.1556616862213229</v>
       </c>
       <c r="T9">
-        <v>1.421420306319067</v>
+        <v>1.431866060955174</v>
       </c>
       <c r="U9">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V9">
         <v>0.34</v>
       </c>
       <c r="W9">
-        <v>0.03583799999999999</v>
+        <v>0.036498</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.298523776378676</v>
+        <v>5.411548117996236</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2184,22 +2184,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1461285913236171</v>
+        <v>0.1456823154082179</v>
       </c>
       <c r="C10">
-        <v>36.88730902941076</v>
+        <v>36.64953286457633</v>
       </c>
       <c r="D10">
-        <v>33.72498902941076</v>
+        <v>33.87567286457633</v>
       </c>
       <c r="E10">
-        <v>3.06168</v>
+        <v>3.45014</v>
       </c>
       <c r="F10">
-        <v>3.10768</v>
+        <v>3.49614</v>
       </c>
       <c r="G10">
         <v>6.27</v>
@@ -2220,28 +2220,28 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M10">
-        <v>0.171854704</v>
+        <v>0.193336542</v>
       </c>
       <c r="N10">
-        <v>0.7581452960000001</v>
+        <v>0.7366634580000002</v>
       </c>
       <c r="O10">
-        <v>0.2577694006400001</v>
+        <v>0.2504655757200001</v>
       </c>
       <c r="P10">
-        <v>0.50037589536</v>
+        <v>0.4861978822800001</v>
       </c>
       <c r="Q10">
-        <v>2.40037589536</v>
+        <v>2.38619788228</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1556616862213229</v>
+        <v>0.1564807641848548</v>
       </c>
       <c r="T10">
-        <v>1.431866060955174</v>
+        <v>1.44254139261625</v>
       </c>
       <c r="U10">
         <v>0.0553</v>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.411548117996236</v>
+        <v>4.810264993774433</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2266,22 +2266,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1456823154082179</v>
+        <v>0.1454010394928187</v>
       </c>
       <c r="C11">
-        <v>36.64953286457633</v>
+        <v>36.35673864219537</v>
       </c>
       <c r="D11">
-        <v>33.87567286457633</v>
+        <v>33.97133864219537</v>
       </c>
       <c r="E11">
-        <v>3.45014</v>
+        <v>3.8386</v>
       </c>
       <c r="F11">
-        <v>3.49614</v>
+        <v>3.884599999999999</v>
       </c>
       <c r="G11">
         <v>6.27</v>
@@ -2302,45 +2302,45 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M11">
-        <v>0.193336542</v>
+        <v>0.22452988</v>
       </c>
       <c r="N11">
-        <v>0.7366634580000002</v>
+        <v>0.7054701200000002</v>
       </c>
       <c r="O11">
-        <v>0.2504655757200001</v>
+        <v>0.2398598408000001</v>
       </c>
       <c r="P11">
-        <v>0.4861978822800001</v>
+        <v>0.4656102792000001</v>
       </c>
       <c r="Q11">
-        <v>2.38619788228</v>
+        <v>2.3656102792</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1564807641848548</v>
+        <v>0.1573180438809097</v>
       </c>
       <c r="T11">
-        <v>1.44254139261625</v>
+        <v>1.453453953869794</v>
       </c>
       <c r="U11">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V11">
         <v>0.34</v>
       </c>
       <c r="W11">
-        <v>0.036498</v>
+        <v>0.038148</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y11">
-        <v>4.810264993774433</v>
+        <v>4.141987694466323</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2348,22 +2348,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1454010394928187</v>
+        <v>0.1452253635774196</v>
       </c>
       <c r="C12">
-        <v>36.35673864219537</v>
+        <v>36.02830302429034</v>
       </c>
       <c r="D12">
-        <v>33.97133864219537</v>
+        <v>34.03136302429034</v>
       </c>
       <c r="E12">
-        <v>3.8386</v>
+        <v>4.22706</v>
       </c>
       <c r="F12">
-        <v>3.8846</v>
+        <v>4.27306</v>
       </c>
       <c r="G12">
         <v>6.27</v>
@@ -2384,45 +2384,45 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M12">
-        <v>0.22452988</v>
+        <v>0.261938578</v>
       </c>
       <c r="N12">
-        <v>0.7054701200000002</v>
+        <v>0.6680614220000001</v>
       </c>
       <c r="O12">
-        <v>0.2398598408000001</v>
+        <v>0.22714088348</v>
       </c>
       <c r="P12">
-        <v>0.4656102792000001</v>
+        <v>0.44092053852</v>
       </c>
       <c r="Q12">
-        <v>2.3656102792</v>
+        <v>2.34092053852</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1573180438809097</v>
+        <v>0.1581741388510332</v>
       </c>
       <c r="T12">
-        <v>1.453453953869794</v>
+        <v>1.464611741218923</v>
       </c>
       <c r="U12">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V12">
         <v>0.34</v>
       </c>
       <c r="W12">
-        <v>0.038148</v>
+        <v>0.04045799999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.141987694466323</v>
+        <v>3.550450670920264</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2430,22 +2430,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1452253635774196</v>
+        <v>0.1450404476620204</v>
       </c>
       <c r="C13">
-        <v>36.02830302429034</v>
+        <v>35.7032540708361</v>
       </c>
       <c r="D13">
-        <v>34.03136302429034</v>
+        <v>34.0947740708361</v>
       </c>
       <c r="E13">
-        <v>4.22706</v>
+        <v>4.615519999999999</v>
       </c>
       <c r="F13">
-        <v>4.27306</v>
+        <v>4.661519999999999</v>
       </c>
       <c r="G13">
         <v>6.27</v>
@@ -2466,45 +2466,45 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M13">
-        <v>0.261938578</v>
+        <v>0.298803432</v>
       </c>
       <c r="N13">
-        <v>0.6680614220000001</v>
+        <v>0.6311965680000002</v>
       </c>
       <c r="O13">
-        <v>0.22714088348</v>
+        <v>0.2146068331200001</v>
       </c>
       <c r="P13">
-        <v>0.44092053852</v>
+        <v>0.4165897348800002</v>
       </c>
       <c r="Q13">
-        <v>2.34092053852</v>
+        <v>2.31658973488</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1581741388510332</v>
+        <v>0.1590496905250232</v>
       </c>
       <c r="T13">
-        <v>1.464611741218923</v>
+        <v>1.47602311464417</v>
       </c>
       <c r="U13">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V13">
         <v>0.34</v>
       </c>
       <c r="W13">
-        <v>0.04045799999999999</v>
+        <v>0.042306</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>3.550450670920264</v>
+        <v>3.112414050184003</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2512,22 +2512,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1450404476620204</v>
+        <v>0.1453214917466213</v>
       </c>
       <c r="C14">
-        <v>35.7032540708361</v>
+        <v>35.21851200753256</v>
       </c>
       <c r="D14">
-        <v>34.0947740708361</v>
+        <v>33.99849200753256</v>
       </c>
       <c r="E14">
-        <v>4.615519999999999</v>
+        <v>5.003979999999999</v>
       </c>
       <c r="F14">
-        <v>4.661519999999999</v>
+        <v>5.04998</v>
       </c>
       <c r="G14">
         <v>6.27</v>
@@ -2548,45 +2548,45 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M14">
-        <v>0.298803432</v>
+        <v>0.363093562</v>
       </c>
       <c r="N14">
-        <v>0.6311965680000002</v>
+        <v>0.5669064380000002</v>
       </c>
       <c r="O14">
-        <v>0.2146068331200001</v>
+        <v>0.1927481889200001</v>
       </c>
       <c r="P14">
-        <v>0.4165897348800002</v>
+        <v>0.3741582490800001</v>
       </c>
       <c r="Q14">
-        <v>2.31658973488</v>
+        <v>2.27415824908</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1590496905250232</v>
+        <v>0.1599453698237026</v>
       </c>
       <c r="T14">
-        <v>1.47602311464417</v>
+        <v>1.487696818492985</v>
       </c>
       <c r="U14">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V14">
         <v>0.34</v>
       </c>
       <c r="W14">
-        <v>0.042306</v>
+        <v>0.047454</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.112414050184003</v>
+        <v>2.561323298814095</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2594,22 +2594,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1453214917466213</v>
+        <v>0.1453451358312221</v>
       </c>
       <c r="C15">
-        <v>35.21851200753256</v>
+        <v>34.82197664338126</v>
       </c>
       <c r="D15">
-        <v>33.99849200753256</v>
+        <v>33.99041664338127</v>
       </c>
       <c r="E15">
-        <v>5.003979999999999</v>
+        <v>5.39244</v>
       </c>
       <c r="F15">
-        <v>5.04998</v>
+        <v>5.43844</v>
       </c>
       <c r="G15">
         <v>6.27</v>
@@ -2630,45 +2630,45 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M15">
-        <v>0.363093562</v>
+        <v>0.412233752</v>
       </c>
       <c r="N15">
-        <v>0.5669064380000002</v>
+        <v>0.5177662480000002</v>
       </c>
       <c r="O15">
-        <v>0.1927481889200001</v>
+        <v>0.1760405243200001</v>
       </c>
       <c r="P15">
-        <v>0.3741582490800001</v>
+        <v>0.3417257236800001</v>
       </c>
       <c r="Q15">
-        <v>2.27415824908</v>
+        <v>2.24172572368</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1599453698237026</v>
+        <v>0.1608618788735141</v>
       </c>
       <c r="T15">
-        <v>1.487696818492985</v>
+        <v>1.499642003826656</v>
       </c>
       <c r="U15">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V15">
         <v>0.34</v>
       </c>
       <c r="W15">
-        <v>0.047454</v>
+        <v>0.050028</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y15">
-        <v>2.561323298814095</v>
+        <v>2.25600159008814</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2676,22 +2676,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1453451358312221</v>
+        <v>0.1450341599158229</v>
       </c>
       <c r="C16">
-        <v>34.82197664338126</v>
+        <v>34.54003440842751</v>
       </c>
       <c r="D16">
-        <v>33.99041664338127</v>
+        <v>34.09693440842751</v>
       </c>
       <c r="E16">
-        <v>5.39244</v>
+        <v>5.7809</v>
       </c>
       <c r="F16">
-        <v>5.43844</v>
+        <v>5.8269</v>
       </c>
       <c r="G16">
         <v>6.27</v>
@@ -2712,28 +2712,28 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M16">
-        <v>0.412233752</v>
+        <v>0.44167902</v>
       </c>
       <c r="N16">
-        <v>0.5177662480000002</v>
+        <v>0.4883209800000001</v>
       </c>
       <c r="O16">
-        <v>0.1760405243200001</v>
+        <v>0.1660291332000001</v>
       </c>
       <c r="P16">
-        <v>0.3417257236800001</v>
+        <v>0.3222918468000001</v>
       </c>
       <c r="Q16">
-        <v>2.24172572368</v>
+        <v>2.2222918468</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1608618788735141</v>
+        <v>0.1617999528421447</v>
       </c>
       <c r="T16">
-        <v>1.499642003826656</v>
+        <v>1.511868252344648</v>
       </c>
       <c r="U16">
         <v>0.07580000000000001</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>2.25600159008814</v>
+        <v>2.105601484082264</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2758,22 +2758,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1450341599158229</v>
+        <v>0.1462227040004238</v>
       </c>
       <c r="C17">
-        <v>34.54003440842751</v>
+        <v>33.74802313884619</v>
       </c>
       <c r="D17">
-        <v>34.09693440842751</v>
+        <v>33.69338313884618</v>
       </c>
       <c r="E17">
-        <v>5.780899999999999</v>
+        <v>6.169359999999999</v>
       </c>
       <c r="F17">
-        <v>5.826899999999999</v>
+        <v>6.21536</v>
       </c>
       <c r="G17">
         <v>6.27</v>
@@ -2794,45 +2794,45 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M17">
-        <v>0.44167902</v>
+        <v>0.5593823999999999</v>
       </c>
       <c r="N17">
-        <v>0.4883209800000002</v>
+        <v>0.3706176000000002</v>
       </c>
       <c r="O17">
-        <v>0.1660291332000001</v>
+        <v>0.1260099840000001</v>
       </c>
       <c r="P17">
-        <v>0.3222918468000001</v>
+        <v>0.2446076160000001</v>
       </c>
       <c r="Q17">
-        <v>2.2222918468</v>
+        <v>2.144607616</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1617999528421447</v>
+        <v>0.1627603619052664</v>
       </c>
       <c r="T17">
-        <v>1.511868252344648</v>
+        <v>1.524385602017832</v>
       </c>
       <c r="U17">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V17">
         <v>0.34</v>
       </c>
       <c r="W17">
-        <v>0.050028</v>
+        <v>0.05939999999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.105601484082265</v>
+        <v>1.662547838473288</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2840,22 +2840,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1462227040004238</v>
+        <v>0.1460054480850246</v>
       </c>
       <c r="C18">
-        <v>33.74802313884619</v>
+        <v>33.43261392537143</v>
       </c>
       <c r="D18">
-        <v>33.69338313884618</v>
+        <v>33.76643392537142</v>
       </c>
       <c r="E18">
-        <v>6.169359999999999</v>
+        <v>6.55782</v>
       </c>
       <c r="F18">
-        <v>6.21536</v>
+        <v>6.60382</v>
       </c>
       <c r="G18">
         <v>6.27</v>
@@ -2876,28 +2876,28 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M18">
-        <v>0.5593823999999999</v>
+        <v>0.5943438</v>
       </c>
       <c r="N18">
-        <v>0.3706176000000002</v>
+        <v>0.3356562000000002</v>
       </c>
       <c r="O18">
-        <v>0.1260099840000001</v>
+        <v>0.1141231080000001</v>
       </c>
       <c r="P18">
-        <v>0.2446076160000001</v>
+        <v>0.2215330920000001</v>
       </c>
       <c r="Q18">
-        <v>2.144607616</v>
+        <v>2.121533092</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1627603619052664</v>
+        <v>0.1637439133554514</v>
       </c>
       <c r="T18">
-        <v>1.524385602017832</v>
+        <v>1.537204574574706</v>
       </c>
       <c r="U18">
         <v>0.09</v>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>1.662547838473288</v>
+        <v>1.564750906798389</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2922,22 +2922,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1460054480850246</v>
+        <v>0.1539779358441705</v>
       </c>
       <c r="C19">
-        <v>33.43261392537143</v>
+        <v>30.55563832337459</v>
       </c>
       <c r="D19">
-        <v>33.76643392537142</v>
+        <v>31.27791832337459</v>
       </c>
       <c r="E19">
-        <v>6.55782</v>
+        <v>6.94628</v>
       </c>
       <c r="F19">
-        <v>6.60382</v>
+        <v>6.99228</v>
       </c>
       <c r="G19">
         <v>6.27</v>
@@ -2958,45 +2958,45 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M19">
-        <v>0.5943438</v>
+        <v>1.026466704</v>
       </c>
       <c r="N19">
-        <v>0.3356562000000002</v>
+        <v>-0.09646670400000001</v>
       </c>
       <c r="O19">
-        <v>0.1141231080000001</v>
+        <v>-0.03279867936000001</v>
       </c>
       <c r="P19">
-        <v>0.2215330920000001</v>
+        <v>-0.06366802464000001</v>
       </c>
       <c r="Q19">
-        <v>2.121533092</v>
+        <v>1.83633197536</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1637439133554514</v>
+        <v>0.1654802073918728</v>
       </c>
       <c r="T19">
-        <v>1.537204574574706</v>
+        <v>1.559834306450314</v>
       </c>
       <c r="U19">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V19">
-        <v>0.34</v>
+        <v>0.3080470109432795</v>
       </c>
       <c r="W19">
-        <v>0.05939999999999999</v>
+        <v>0.1015786987935266</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y19">
-        <v>1.564750906798389</v>
+        <v>0.9060206204214102</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3004,22 +3004,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1539779358441705</v>
+        <v>0.1549879358441705</v>
       </c>
       <c r="C20">
-        <v>30.55563832337457</v>
+        <v>29.87785425783226</v>
       </c>
       <c r="D20">
-        <v>31.27791832337458</v>
+        <v>30.98859425783226</v>
       </c>
       <c r="E20">
-        <v>6.946279999999999</v>
+        <v>7.334739999999999</v>
       </c>
       <c r="F20">
-        <v>6.992279999999999</v>
+        <v>7.380739999999999</v>
       </c>
       <c r="G20">
         <v>6.27</v>
@@ -3040,37 +3040,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M20">
-        <v>1.026466704</v>
+        <v>1.083492632</v>
       </c>
       <c r="N20">
-        <v>-0.09646670399999979</v>
+        <v>-0.1534926319999999</v>
       </c>
       <c r="O20">
-        <v>-0.03279867935999993</v>
+        <v>-0.05218749487999996</v>
       </c>
       <c r="P20">
-        <v>-0.06366802463999986</v>
+        <v>-0.1013051371199999</v>
       </c>
       <c r="Q20">
-        <v>1.83633197536</v>
+        <v>1.79869486288</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1654802073918728</v>
+        <v>0.1669577408164639</v>
       </c>
       <c r="T20">
-        <v>1.559834306450314</v>
+        <v>1.579091520110194</v>
       </c>
       <c r="U20">
         <v>0.1468</v>
       </c>
       <c r="V20">
-        <v>0.3080470109432796</v>
+        <v>0.2918340103673174</v>
       </c>
       <c r="W20">
-        <v>0.1015786987935266</v>
+        <v>0.1039587672780778</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.9060206204214104</v>
+        <v>0.8583353246097571</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3086,22 +3086,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1549879358441705</v>
+        <v>0.1559979358441705</v>
       </c>
       <c r="C21">
-        <v>29.87785425783226</v>
+        <v>29.20537369101631</v>
       </c>
       <c r="D21">
-        <v>30.98859425783226</v>
+        <v>30.7045736910163</v>
       </c>
       <c r="E21">
-        <v>7.334739999999999</v>
+        <v>7.723199999999999</v>
       </c>
       <c r="F21">
-        <v>7.380739999999999</v>
+        <v>7.7692</v>
       </c>
       <c r="G21">
         <v>6.27</v>
@@ -3122,37 +3122,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M21">
-        <v>1.083492632</v>
+        <v>1.14051856</v>
       </c>
       <c r="N21">
-        <v>-0.1534926319999999</v>
+        <v>-0.2105185599999999</v>
       </c>
       <c r="O21">
-        <v>-0.05218749487999996</v>
+        <v>-0.07157631039999997</v>
       </c>
       <c r="P21">
-        <v>-0.1013051371199999</v>
+        <v>-0.1389422496</v>
       </c>
       <c r="Q21">
-        <v>1.79869486288</v>
+        <v>1.7610577504</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1669577408164639</v>
+        <v>0.1684722125766697</v>
       </c>
       <c r="T21">
-        <v>1.579091520110194</v>
+        <v>1.598830164111572</v>
       </c>
       <c r="U21">
         <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.2918340103673174</v>
+        <v>0.2772423098489515</v>
       </c>
       <c r="W21">
-        <v>0.1039587672780778</v>
+        <v>0.1061008289141739</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.8583353246097571</v>
+        <v>0.8154185583792692</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3168,22 +3168,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1559979358441705</v>
+        <v>0.1698972164398659</v>
       </c>
       <c r="C22">
-        <v>29.20537369101631</v>
+        <v>25.37790435989691</v>
       </c>
       <c r="D22">
-        <v>30.7045736910163</v>
+        <v>27.26556435989691</v>
       </c>
       <c r="E22">
-        <v>7.723199999999999</v>
+        <v>8.111660000000001</v>
       </c>
       <c r="F22">
-        <v>7.7692</v>
+        <v>8.15766</v>
       </c>
       <c r="G22">
         <v>6.27</v>
@@ -3204,45 +3204,45 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M22">
-        <v>1.14051856</v>
+        <v>1.638058128</v>
       </c>
       <c r="N22">
-        <v>-0.2105185599999999</v>
+        <v>-0.7080581279999998</v>
       </c>
       <c r="O22">
-        <v>-0.07157631039999997</v>
+        <v>-0.24073976352</v>
       </c>
       <c r="P22">
-        <v>-0.1389422496</v>
+        <v>-0.4673183644799999</v>
       </c>
       <c r="Q22">
-        <v>1.7610577504</v>
+        <v>1.43268163552</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1684722125766697</v>
+        <v>0.1719861400721913</v>
       </c>
       <c r="T22">
-        <v>1.598830164111572</v>
+        <v>1.644628419122499</v>
       </c>
       <c r="U22">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V22">
-        <v>0.2772423098489515</v>
+        <v>0.1930334428278604</v>
       </c>
       <c r="W22">
-        <v>0.1061008289141739</v>
+        <v>0.1620388846801656</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y22">
-        <v>0.8154185583792692</v>
+        <v>0.5677454200819424</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3250,22 +3250,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1698972164398659</v>
+        <v>0.1714472164398659</v>
       </c>
       <c r="C23">
-        <v>25.37790435989692</v>
+        <v>24.65309289939268</v>
       </c>
       <c r="D23">
-        <v>27.26556435989692</v>
+        <v>26.92921289939268</v>
       </c>
       <c r="E23">
-        <v>8.111659999999999</v>
+        <v>8.500120000000001</v>
       </c>
       <c r="F23">
-        <v>8.157659999999998</v>
+        <v>8.54612</v>
       </c>
       <c r="G23">
         <v>6.27</v>
@@ -3286,37 +3286,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M23">
-        <v>1.638058128</v>
+        <v>1.716060896</v>
       </c>
       <c r="N23">
-        <v>-0.7080581279999996</v>
+        <v>-0.786060896</v>
       </c>
       <c r="O23">
-        <v>-0.2407397635199999</v>
+        <v>-0.26726070464</v>
       </c>
       <c r="P23">
-        <v>-0.4673183644799997</v>
+        <v>-0.51880019136</v>
       </c>
       <c r="Q23">
-        <v>1.43268163552</v>
+        <v>1.38119980864</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1719861400721912</v>
+        <v>0.1736039110987578</v>
       </c>
       <c r="T23">
-        <v>1.644628419122499</v>
+        <v>1.665713398854838</v>
       </c>
       <c r="U23">
         <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.1930334428278605</v>
+        <v>0.184259195426594</v>
       </c>
       <c r="W23">
-        <v>0.1620388846801656</v>
+        <v>0.1638007535583399</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.5677454200819425</v>
+        <v>0.5419388100782176</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3332,22 +3332,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1714472164398659</v>
+        <v>0.1729972164398659</v>
       </c>
       <c r="C24">
-        <v>24.65309289939268</v>
+        <v>23.93647886298897</v>
       </c>
       <c r="D24">
-        <v>26.92921289939268</v>
+        <v>26.60105886298897</v>
       </c>
       <c r="E24">
-        <v>8.500120000000001</v>
+        <v>8.888580000000001</v>
       </c>
       <c r="F24">
-        <v>8.54612</v>
+        <v>8.93458</v>
       </c>
       <c r="G24">
         <v>6.27</v>
@@ -3368,37 +3368,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M24">
-        <v>1.716060896</v>
+        <v>1.794063664</v>
       </c>
       <c r="N24">
-        <v>-0.786060896</v>
+        <v>-0.8640636639999999</v>
       </c>
       <c r="O24">
-        <v>-0.26726070464</v>
+        <v>-0.29378164576</v>
       </c>
       <c r="P24">
-        <v>-0.51880019136</v>
+        <v>-0.5702820182399999</v>
       </c>
       <c r="Q24">
-        <v>1.38119980864</v>
+        <v>1.32971798176</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1736039110987578</v>
+        <v>0.1752637021519884</v>
       </c>
       <c r="T24">
-        <v>1.665713398854838</v>
+        <v>1.687346040398408</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.184259195426594</v>
+        <v>0.1762479260602204</v>
       </c>
       <c r="W24">
-        <v>0.1638007535583399</v>
+        <v>0.1654094164471078</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.5419388100782176</v>
+        <v>0.5183762531182952</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3414,22 +3414,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1729972164398659</v>
+        <v>0.1835723698734633</v>
       </c>
       <c r="C25">
-        <v>23.93647886298897</v>
+        <v>21.50617056473705</v>
       </c>
       <c r="D25">
-        <v>26.60105886298897</v>
+        <v>24.55921056473705</v>
       </c>
       <c r="E25">
-        <v>8.888580000000001</v>
+        <v>9.277040000000001</v>
       </c>
       <c r="F25">
-        <v>8.93458</v>
+        <v>9.323040000000001</v>
       </c>
       <c r="G25">
         <v>6.27</v>
@@ -3450,45 +3450,45 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M25">
-        <v>1.794063664</v>
+        <v>2.198372832</v>
       </c>
       <c r="N25">
-        <v>-0.8640636639999999</v>
+        <v>-1.268372832</v>
       </c>
       <c r="O25">
-        <v>-0.29378164576</v>
+        <v>-0.4312467628800001</v>
       </c>
       <c r="P25">
-        <v>-0.5702820182399999</v>
+        <v>-0.8371260691200002</v>
       </c>
       <c r="Q25">
-        <v>1.32971798176</v>
+        <v>1.06287393088</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1752637021519884</v>
+        <v>0.1777897422245112</v>
       </c>
       <c r="T25">
-        <v>1.687346040398408</v>
+        <v>1.720268810591208</v>
       </c>
       <c r="U25">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.1762479260602204</v>
+        <v>0.1438336552368748</v>
       </c>
       <c r="W25">
-        <v>0.1654094164471078</v>
+        <v>0.2018840240951449</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y25">
-        <v>0.5183762531182952</v>
+        <v>0.4230401624613963</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3496,22 +3496,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1835723698734633</v>
+        <v>0.1854723698734633</v>
       </c>
       <c r="C26">
-        <v>21.50617056473706</v>
+        <v>20.78362516105074</v>
       </c>
       <c r="D26">
-        <v>24.55921056473706</v>
+        <v>24.22512516105073</v>
       </c>
       <c r="E26">
-        <v>9.27704</v>
+        <v>9.6655</v>
       </c>
       <c r="F26">
-        <v>9.323039999999999</v>
+        <v>9.711499999999999</v>
       </c>
       <c r="G26">
         <v>6.27</v>
@@ -3532,37 +3532,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M26">
-        <v>2.198372832</v>
+        <v>2.2899717</v>
       </c>
       <c r="N26">
-        <v>-1.268372832</v>
+        <v>-1.3599717</v>
       </c>
       <c r="O26">
-        <v>-0.43124676288</v>
+        <v>-0.4623903779999999</v>
       </c>
       <c r="P26">
-        <v>-0.8371260691199999</v>
+        <v>-0.8975813219999997</v>
       </c>
       <c r="Q26">
-        <v>1.06287393088</v>
+        <v>1.002418678</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1777897422245112</v>
+        <v>0.1795496054541713</v>
       </c>
       <c r="T26">
-        <v>1.720268810591208</v>
+        <v>1.743205728065757</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.1438336552368748</v>
+        <v>0.1380803090273998</v>
       </c>
       <c r="W26">
-        <v>0.2018840240951449</v>
+        <v>0.2032406631313391</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.4230401624613964</v>
+        <v>0.4061185559629407</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1854723698734633</v>
+        <v>0.1873723698734633</v>
       </c>
       <c r="C27">
-        <v>20.78362516105074</v>
+        <v>20.07004707588245</v>
       </c>
       <c r="D27">
-        <v>24.22512516105073</v>
+        <v>23.90000707588245</v>
       </c>
       <c r="E27">
-        <v>9.6655</v>
+        <v>10.05396</v>
       </c>
       <c r="F27">
-        <v>9.711499999999999</v>
+        <v>10.09996</v>
       </c>
       <c r="G27">
         <v>6.27</v>
@@ -3614,37 +3614,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M27">
-        <v>2.2899717</v>
+        <v>2.381570568</v>
       </c>
       <c r="N27">
-        <v>-1.3599717</v>
+        <v>-1.451570568</v>
       </c>
       <c r="O27">
-        <v>-0.4623903779999999</v>
+        <v>-0.49353399312</v>
       </c>
       <c r="P27">
-        <v>-0.8975813219999997</v>
+        <v>-0.9580365748799997</v>
       </c>
       <c r="Q27">
-        <v>1.002418678</v>
+        <v>0.9419634251200002</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1795496054541713</v>
+        <v>0.1813570325549034</v>
       </c>
       <c r="T27">
-        <v>1.743205728065757</v>
+        <v>1.766762562228808</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.1380803090273998</v>
+        <v>0.1327695279109614</v>
       </c>
       <c r="W27">
-        <v>0.2032406631313391</v>
+        <v>0.2044929453185953</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.4061185559629407</v>
+        <v>0.3904986115028275</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3660,22 +3660,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1873723698734633</v>
+        <v>0.1892723698734633</v>
       </c>
       <c r="C28">
-        <v>20.07004707588245</v>
+        <v>19.36508004749624</v>
       </c>
       <c r="D28">
-        <v>23.90000707588245</v>
+        <v>23.58350004749624</v>
       </c>
       <c r="E28">
-        <v>10.05396</v>
+        <v>10.44242</v>
       </c>
       <c r="F28">
-        <v>10.09996</v>
+        <v>10.48842</v>
       </c>
       <c r="G28">
         <v>6.27</v>
@@ -3696,37 +3696,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M28">
-        <v>2.381570568</v>
+        <v>2.473169436</v>
       </c>
       <c r="N28">
-        <v>-1.451570568</v>
+        <v>-1.543169436</v>
       </c>
       <c r="O28">
-        <v>-0.49353399312</v>
+        <v>-0.52467760824</v>
       </c>
       <c r="P28">
-        <v>-0.9580365748799997</v>
+        <v>-1.01849182776</v>
       </c>
       <c r="Q28">
-        <v>0.9419634251200002</v>
+        <v>0.88150817224</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1813570325549034</v>
+        <v>0.1832139782063404</v>
       </c>
       <c r="T28">
-        <v>1.766762562228808</v>
+        <v>1.790964789108655</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.1327695279109614</v>
+        <v>0.1278521379883331</v>
       </c>
       <c r="W28">
-        <v>0.2044929453185953</v>
+        <v>0.2056524658623511</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3904986115028275</v>
+        <v>0.3760356999656858</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3742,22 +3742,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1892723698734633</v>
+        <v>0.1911723698734633</v>
       </c>
       <c r="C29">
-        <v>19.36508004749624</v>
+        <v>18.6683864393543</v>
       </c>
       <c r="D29">
-        <v>23.58350004749624</v>
+        <v>23.2752664393543</v>
       </c>
       <c r="E29">
-        <v>10.44242</v>
+        <v>10.83088</v>
       </c>
       <c r="F29">
-        <v>10.48842</v>
+        <v>10.87688</v>
       </c>
       <c r="G29">
         <v>6.27</v>
@@ -3778,37 +3778,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M29">
-        <v>2.473169436</v>
+        <v>2.564768304</v>
       </c>
       <c r="N29">
-        <v>-1.543169436</v>
+        <v>-1.634768304</v>
       </c>
       <c r="O29">
-        <v>-0.52467760824</v>
+        <v>-0.5558212233600001</v>
       </c>
       <c r="P29">
-        <v>-1.01849182776</v>
+        <v>-1.07894708064</v>
       </c>
       <c r="Q29">
-        <v>0.88150817224</v>
+        <v>0.82105291936</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1832139782063404</v>
+        <v>0.1851225056814285</v>
       </c>
       <c r="T29">
-        <v>1.790964789108655</v>
+        <v>1.815839300068497</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.1278521379883331</v>
+        <v>0.1232859902030355</v>
       </c>
       <c r="W29">
-        <v>0.2056524658623511</v>
+        <v>0.2067291635101242</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3760356999656858</v>
+        <v>0.3626058535383397</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3824,22 +3824,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1911723698734633</v>
+        <v>0.1930723698734633</v>
       </c>
       <c r="C30">
-        <v>18.6683864393543</v>
+        <v>17.97964603867377</v>
       </c>
       <c r="D30">
-        <v>23.2752664393543</v>
+        <v>22.97498603867377</v>
       </c>
       <c r="E30">
-        <v>10.83088</v>
+        <v>11.21934</v>
       </c>
       <c r="F30">
-        <v>10.87688</v>
+        <v>11.26534</v>
       </c>
       <c r="G30">
         <v>6.27</v>
@@ -3860,37 +3860,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M30">
-        <v>2.564768304</v>
+        <v>2.656367172</v>
       </c>
       <c r="N30">
-        <v>-1.634768304</v>
+        <v>-1.726367172</v>
       </c>
       <c r="O30">
-        <v>-0.5558212233600001</v>
+        <v>-0.5869648384799999</v>
       </c>
       <c r="P30">
-        <v>-1.07894708064</v>
+        <v>-1.13940233352</v>
       </c>
       <c r="Q30">
-        <v>0.82105291936</v>
+        <v>0.76059766648</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1851225056814285</v>
+        <v>0.187084794493843</v>
       </c>
       <c r="T30">
-        <v>1.815839300068497</v>
+        <v>1.841414501477913</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.1232859902030355</v>
+        <v>0.1190347491615516</v>
       </c>
       <c r="W30">
-        <v>0.2067291635101242</v>
+        <v>0.2077316061477062</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3626058535383397</v>
+        <v>0.3501022034163281</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3906,22 +3906,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1930723698734633</v>
+        <v>0.1949723698734633</v>
       </c>
       <c r="C31">
-        <v>17.97964603867378</v>
+        <v>17.29855494679994</v>
       </c>
       <c r="D31">
-        <v>22.97498603867378</v>
+        <v>22.68235494679994</v>
       </c>
       <c r="E31">
-        <v>11.21934</v>
+        <v>11.6078</v>
       </c>
       <c r="F31">
-        <v>11.26534</v>
+        <v>11.6538</v>
       </c>
       <c r="G31">
         <v>6.27</v>
@@ -3942,37 +3942,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M31">
-        <v>2.656367171999999</v>
+        <v>2.74796604</v>
       </c>
       <c r="N31">
-        <v>-1.726367171999999</v>
+        <v>-1.81796604</v>
       </c>
       <c r="O31">
-        <v>-0.5869648384799998</v>
+        <v>-0.6181084535999999</v>
       </c>
       <c r="P31">
-        <v>-1.13940233352</v>
+        <v>-1.1998575864</v>
       </c>
       <c r="Q31">
-        <v>0.7605976664800003</v>
+        <v>0.7001424136000003</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.187084794493843</v>
+        <v>0.1891031487008979</v>
       </c>
       <c r="T31">
-        <v>1.841414501477913</v>
+        <v>1.867720422927597</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.1190347491615516</v>
+        <v>0.1150669241894999</v>
       </c>
       <c r="W31">
-        <v>0.2077316061477062</v>
+        <v>0.208667219276116</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3501022034163281</v>
+        <v>0.3384321299691172</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3988,22 +3988,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1949723698734633</v>
+        <v>0.1968723698734633</v>
       </c>
       <c r="C32">
-        <v>17.29855494679994</v>
+        <v>16.62482455331225</v>
       </c>
       <c r="D32">
-        <v>22.68235494679994</v>
+        <v>22.39708455331225</v>
       </c>
       <c r="E32">
-        <v>11.6078</v>
+        <v>11.99626</v>
       </c>
       <c r="F32">
-        <v>11.6538</v>
+        <v>12.04226</v>
       </c>
       <c r="G32">
         <v>6.27</v>
@@ -4024,37 +4024,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M32">
-        <v>2.74796604</v>
+        <v>2.839564908</v>
       </c>
       <c r="N32">
-        <v>-1.81796604</v>
+        <v>-1.909564908</v>
       </c>
       <c r="O32">
-        <v>-0.6181084535999999</v>
+        <v>-0.64925206872</v>
       </c>
       <c r="P32">
-        <v>-1.1998575864</v>
+        <v>-1.26031283928</v>
       </c>
       <c r="Q32">
-        <v>0.7001424136000003</v>
+        <v>0.6396871607200003</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1891031487008979</v>
+        <v>0.1911800059284471</v>
       </c>
       <c r="T32">
-        <v>1.867720422927597</v>
+        <v>1.894788834854084</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.1150669241894999</v>
+        <v>0.1113550879253224</v>
       </c>
       <c r="W32">
-        <v>0.208667219276116</v>
+        <v>0.209542470267209</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3384321299691172</v>
+        <v>0.3275149644862424</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4070,22 +4070,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1968723698734633</v>
+        <v>0.1987723698734633</v>
       </c>
       <c r="C33">
-        <v>16.62482455331225</v>
+        <v>15.95818058658353</v>
       </c>
       <c r="D33">
-        <v>22.39708455331225</v>
+        <v>22.11890058658353</v>
       </c>
       <c r="E33">
-        <v>11.99626</v>
+        <v>12.38472</v>
       </c>
       <c r="F33">
-        <v>12.04226</v>
+        <v>12.43072</v>
       </c>
       <c r="G33">
         <v>6.27</v>
@@ -4106,37 +4106,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M33">
-        <v>2.839564908</v>
+        <v>2.931163776</v>
       </c>
       <c r="N33">
-        <v>-1.909564908</v>
+        <v>-2.001163776</v>
       </c>
       <c r="O33">
-        <v>-0.64925206872</v>
+        <v>-0.68039568384</v>
       </c>
       <c r="P33">
-        <v>-1.26031283928</v>
+        <v>-1.32076809216</v>
       </c>
       <c r="Q33">
-        <v>0.6396871607200003</v>
+        <v>0.5792319078400001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1911800059284471</v>
+        <v>0.1933179471921007</v>
       </c>
       <c r="T33">
-        <v>1.894788834854084</v>
+        <v>1.922653376543115</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.1113550879253224</v>
+        <v>0.1078752414276561</v>
       </c>
       <c r="W33">
-        <v>0.209542470267209</v>
+        <v>0.2103630180713587</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3275149644862424</v>
+        <v>0.3172801218460474</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4152,22 +4152,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1987723698734633</v>
+        <v>0.2006723698734633</v>
       </c>
       <c r="C34">
-        <v>15.95818058658353</v>
+        <v>15.29836223422639</v>
       </c>
       <c r="D34">
-        <v>22.11890058658353</v>
+        <v>21.84754223422639</v>
       </c>
       <c r="E34">
-        <v>12.38472</v>
+        <v>12.77318</v>
       </c>
       <c r="F34">
-        <v>12.43072</v>
+        <v>12.81918</v>
       </c>
       <c r="G34">
         <v>6.27</v>
@@ -4188,37 +4188,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M34">
-        <v>2.931163776</v>
+        <v>3.022762644</v>
       </c>
       <c r="N34">
-        <v>-2.001163776</v>
+        <v>-2.092762644</v>
       </c>
       <c r="O34">
-        <v>-0.68039568384</v>
+        <v>-0.71153929896</v>
       </c>
       <c r="P34">
-        <v>-1.32076809216</v>
+        <v>-1.38122334504</v>
       </c>
       <c r="Q34">
-        <v>0.5792319078400001</v>
+        <v>0.5187766549599999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1933179471921007</v>
+        <v>0.195519707597953</v>
       </c>
       <c r="T34">
-        <v>1.922653376543115</v>
+        <v>1.951349695595997</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.1078752414276561</v>
+        <v>0.1046062947177271</v>
       </c>
       <c r="W34">
-        <v>0.2103630180713587</v>
+        <v>0.21113383570556</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3172801218460474</v>
+        <v>0.3076655726991974</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4234,22 +4234,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2006723698734633</v>
+        <v>0.2025723698734633</v>
       </c>
       <c r="C35">
-        <v>15.29836223422639</v>
+        <v>14.64512132749816</v>
       </c>
       <c r="D35">
-        <v>21.84754223422639</v>
+        <v>21.58276132749816</v>
       </c>
       <c r="E35">
-        <v>12.77318</v>
+        <v>13.16164</v>
       </c>
       <c r="F35">
-        <v>12.81918</v>
+        <v>13.20764</v>
       </c>
       <c r="G35">
         <v>6.27</v>
@@ -4270,37 +4270,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M35">
-        <v>3.022762644</v>
+        <v>3.114361512</v>
       </c>
       <c r="N35">
-        <v>-2.092762644</v>
+        <v>-2.184361512</v>
       </c>
       <c r="O35">
-        <v>-0.71153929896</v>
+        <v>-0.74268291408</v>
       </c>
       <c r="P35">
-        <v>-1.38122334504</v>
+        <v>-1.44167859792</v>
       </c>
       <c r="Q35">
-        <v>0.5187766549599999</v>
+        <v>0.4583214020800002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.195519707597953</v>
+        <v>0.1977881880161038</v>
       </c>
       <c r="T35">
-        <v>1.951349695595997</v>
+        <v>1.980915600074724</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.1046062947177271</v>
+        <v>0.1015296389907352</v>
       </c>
       <c r="W35">
-        <v>0.21113383570556</v>
+        <v>0.2118593111259847</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3076655726991974</v>
+        <v>0.2986165852668681</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4316,22 +4316,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2025723698734633</v>
+        <v>0.2044723698734633</v>
       </c>
       <c r="C36">
-        <v>14.64512132749816</v>
+        <v>13.99822158430311</v>
       </c>
       <c r="D36">
-        <v>21.58276132749816</v>
+        <v>21.32432158430311</v>
       </c>
       <c r="E36">
-        <v>13.16164</v>
+        <v>13.5501</v>
       </c>
       <c r="F36">
-        <v>13.20764</v>
+        <v>13.5961</v>
       </c>
       <c r="G36">
         <v>6.27</v>
@@ -4352,37 +4352,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M36">
-        <v>3.114361512</v>
+        <v>3.20596038</v>
       </c>
       <c r="N36">
-        <v>-2.184361512</v>
+        <v>-2.27596038</v>
       </c>
       <c r="O36">
-        <v>-0.74268291408</v>
+        <v>-0.7738265292000001</v>
       </c>
       <c r="P36">
-        <v>-1.44167859792</v>
+        <v>-1.5021338508</v>
       </c>
       <c r="Q36">
-        <v>0.4583214020800002</v>
+        <v>0.3978661492</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1977881880161038</v>
+        <v>0.2001264678317362</v>
       </c>
       <c r="T36">
-        <v>1.980915600074724</v>
+        <v>2.011391224691259</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.1015296389907352</v>
+        <v>0.09862879216242844</v>
       </c>
       <c r="W36">
-        <v>0.2118593111259847</v>
+        <v>0.2125433308080994</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2986165852668681</v>
+        <v>0.2900846828306718</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4398,22 +4398,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2044723698734633</v>
+        <v>0.2063723698734633</v>
       </c>
       <c r="C37">
-        <v>13.99822158430311</v>
+        <v>13.35743790593862</v>
       </c>
       <c r="D37">
-        <v>21.32432158430311</v>
+        <v>21.07199790593862</v>
       </c>
       <c r="E37">
-        <v>13.5501</v>
+        <v>13.93856</v>
       </c>
       <c r="F37">
-        <v>13.5961</v>
+        <v>13.98456</v>
       </c>
       <c r="G37">
         <v>6.27</v>
@@ -4434,37 +4434,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M37">
-        <v>3.20596038</v>
+        <v>3.297559248</v>
       </c>
       <c r="N37">
-        <v>-2.27596038</v>
+        <v>-2.367559248</v>
       </c>
       <c r="O37">
-        <v>-0.7738265292000001</v>
+        <v>-0.80497014432</v>
       </c>
       <c r="P37">
-        <v>-1.5021338508</v>
+        <v>-1.56258910368</v>
       </c>
       <c r="Q37">
-        <v>0.3978661492</v>
+        <v>0.3374108963199998</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2001264678317362</v>
+        <v>0.202537818891607</v>
       </c>
       <c r="T37">
-        <v>2.011391224691259</v>
+        <v>2.042819212577059</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.09862879216242844</v>
+        <v>0.09588910349124985</v>
       </c>
       <c r="W37">
-        <v>0.2125433308080994</v>
+        <v>0.2131893493967633</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2900846828306718</v>
+        <v>0.2820267749742643</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4480,22 +4480,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2063723698734633</v>
+        <v>0.2082723698734633</v>
       </c>
       <c r="C38">
-        <v>13.35743790593862</v>
+        <v>12.72255572318555</v>
       </c>
       <c r="D38">
-        <v>21.07199790593862</v>
+        <v>20.82557572318555</v>
       </c>
       <c r="E38">
-        <v>13.93856</v>
+        <v>14.32702</v>
       </c>
       <c r="F38">
-        <v>13.98456</v>
+        <v>14.37302</v>
       </c>
       <c r="G38">
         <v>6.27</v>
@@ -4516,37 +4516,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M38">
-        <v>3.297559248</v>
+        <v>3.389158116</v>
       </c>
       <c r="N38">
-        <v>-2.367559248</v>
+        <v>-2.459158116</v>
       </c>
       <c r="O38">
-        <v>-0.8049701443199999</v>
+        <v>-0.83611375944</v>
       </c>
       <c r="P38">
-        <v>-1.56258910368</v>
+        <v>-1.62304435656</v>
       </c>
       <c r="Q38">
-        <v>0.3374108963200002</v>
+        <v>0.27695564344</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.202537818891607</v>
+        <v>0.2050257207787754</v>
       </c>
       <c r="T38">
-        <v>2.042819212577059</v>
+        <v>2.075244914363997</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.09588910349124988</v>
+        <v>0.09329750609959447</v>
       </c>
       <c r="W38">
-        <v>0.2131893493967633</v>
+        <v>0.2138004480617156</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2820267749742643</v>
+        <v>0.2744044297046896</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4562,22 +4562,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2082723698734633</v>
+        <v>0.2101723698734633</v>
       </c>
       <c r="C39">
-        <v>12.72255572318555</v>
+        <v>12.09337038775045</v>
       </c>
       <c r="D39">
-        <v>20.82557572318555</v>
+        <v>20.58485038775045</v>
       </c>
       <c r="E39">
-        <v>14.32702</v>
+        <v>14.71548</v>
       </c>
       <c r="F39">
-        <v>14.37302</v>
+        <v>14.76148</v>
       </c>
       <c r="G39">
         <v>6.27</v>
@@ -4598,37 +4598,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M39">
-        <v>3.389158116</v>
+        <v>3.480756984</v>
       </c>
       <c r="N39">
-        <v>-2.459158116</v>
+        <v>-2.550756984</v>
       </c>
       <c r="O39">
-        <v>-0.83611375944</v>
+        <v>-0.8672573745599998</v>
       </c>
       <c r="P39">
-        <v>-1.62304435656</v>
+        <v>-1.68349960944</v>
       </c>
       <c r="Q39">
-        <v>0.27695564344</v>
+        <v>0.2165003905600003</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2050257207787754</v>
+        <v>0.2075938775655299</v>
       </c>
       <c r="T39">
-        <v>2.075244914363997</v>
+        <v>2.108716606531158</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.09329750609959447</v>
+        <v>0.09084230857065778</v>
       </c>
       <c r="W39">
-        <v>0.2138004480617156</v>
+        <v>0.2143793836390389</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2744044297046896</v>
+        <v>0.2671832605019346</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4644,22 +4644,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2101723698734633</v>
+        <v>0.2120723698734633</v>
       </c>
       <c r="C40">
-        <v>12.09337038775045</v>
+        <v>11.46968660543177</v>
       </c>
       <c r="D40">
-        <v>20.58485038775045</v>
+        <v>20.34962660543177</v>
       </c>
       <c r="E40">
-        <v>14.71548</v>
+        <v>15.10394</v>
       </c>
       <c r="F40">
-        <v>14.76148</v>
+        <v>15.14994</v>
       </c>
       <c r="G40">
         <v>6.27</v>
@@ -4680,37 +4680,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M40">
-        <v>3.480756984</v>
+        <v>3.572355852</v>
       </c>
       <c r="N40">
-        <v>-2.550756984</v>
+        <v>-2.642355852</v>
       </c>
       <c r="O40">
-        <v>-0.8672573745599998</v>
+        <v>-0.8984009896799999</v>
       </c>
       <c r="P40">
-        <v>-1.68349960944</v>
+        <v>-1.74395486232</v>
       </c>
       <c r="Q40">
-        <v>0.2165003905600003</v>
+        <v>0.1560451376800001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2075938775655299</v>
+        <v>0.2102462362141451</v>
       </c>
       <c r="T40">
-        <v>2.108716606531158</v>
+        <v>2.14328573122839</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.09084230857065778</v>
+        <v>0.08851301860730756</v>
       </c>
       <c r="W40">
-        <v>0.2143793836390389</v>
+        <v>0.2149286302123969</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2671832605019346</v>
+        <v>0.2603324076685517</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4726,22 +4726,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2120723698734633</v>
+        <v>0.2139723698734633</v>
       </c>
       <c r="C41">
-        <v>11.46968660543177</v>
+        <v>10.85131790771043</v>
       </c>
       <c r="D41">
-        <v>20.34962660543177</v>
+        <v>20.11971790771043</v>
       </c>
       <c r="E41">
-        <v>15.10394</v>
+        <v>15.4924</v>
       </c>
       <c r="F41">
-        <v>15.14994</v>
+        <v>15.5384</v>
       </c>
       <c r="G41">
         <v>6.27</v>
@@ -4762,37 +4762,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M41">
-        <v>3.572355852</v>
+        <v>3.66395472</v>
       </c>
       <c r="N41">
-        <v>-2.642355852</v>
+        <v>-2.73395472</v>
       </c>
       <c r="O41">
-        <v>-0.8984009896799999</v>
+        <v>-0.9295446048</v>
       </c>
       <c r="P41">
-        <v>-1.74395486232</v>
+        <v>-1.8044101152</v>
       </c>
       <c r="Q41">
-        <v>0.1560451376800001</v>
+        <v>0.09558988480000008</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2102462362141451</v>
+        <v>0.2129870068177142</v>
       </c>
       <c r="T41">
-        <v>2.14328573122839</v>
+        <v>2.179007160082196</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.08851301860730756</v>
+        <v>0.08630019314212488</v>
       </c>
       <c r="W41">
-        <v>0.2149286302123969</v>
+        <v>0.215450414457087</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2603324076685517</v>
+        <v>0.2538240974768379</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4808,22 +4808,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2139723698734633</v>
+        <v>0.2158723698734633</v>
       </c>
       <c r="C42">
-        <v>10.85131790771043</v>
+        <v>10.23808615875972</v>
       </c>
       <c r="D42">
-        <v>20.11971790771043</v>
+        <v>19.89494615875972</v>
       </c>
       <c r="E42">
-        <v>15.4924</v>
+        <v>15.88086</v>
       </c>
       <c r="F42">
-        <v>15.5384</v>
+        <v>15.92686</v>
       </c>
       <c r="G42">
         <v>6.27</v>
@@ -4844,37 +4844,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M42">
-        <v>3.66395472</v>
+        <v>3.755553588</v>
       </c>
       <c r="N42">
-        <v>-2.73395472</v>
+        <v>-2.825553588</v>
       </c>
       <c r="O42">
-        <v>-0.9295446048</v>
+        <v>-0.9606882199200001</v>
       </c>
       <c r="P42">
-        <v>-1.8044101152</v>
+        <v>-1.86486536808</v>
       </c>
       <c r="Q42">
-        <v>0.09558988480000008</v>
+        <v>0.0351346319200001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2129870068177142</v>
+        <v>0.2158206848993703</v>
       </c>
       <c r="T42">
-        <v>2.179007160082196</v>
+        <v>2.215939484829352</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.08630019314212488</v>
+        <v>0.08419531038256085</v>
       </c>
       <c r="W42">
-        <v>0.215450414457087</v>
+        <v>0.2159467458117922</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2538240974768379</v>
+        <v>0.2476332658310613</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4890,22 +4890,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2158723698734633</v>
+        <v>0.2177723698734633</v>
       </c>
       <c r="C43">
-        <v>10.23808615875972</v>
+        <v>9.629821095135505</v>
       </c>
       <c r="D43">
-        <v>19.89494615875972</v>
+        <v>19.6751410951355</v>
       </c>
       <c r="E43">
-        <v>15.88086</v>
+        <v>16.26932</v>
       </c>
       <c r="F43">
-        <v>15.92686</v>
+        <v>16.31532</v>
       </c>
       <c r="G43">
         <v>6.27</v>
@@ -4926,37 +4926,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M43">
-        <v>3.755553588</v>
+        <v>3.847152456</v>
       </c>
       <c r="N43">
-        <v>-2.825553588</v>
+        <v>-2.917152456</v>
       </c>
       <c r="O43">
-        <v>-0.9606882199200001</v>
+        <v>-0.9918318350400002</v>
       </c>
       <c r="P43">
-        <v>-1.86486536808</v>
+        <v>-1.92532062096</v>
       </c>
       <c r="Q43">
-        <v>0.0351346319200001</v>
+        <v>-0.0253206209600001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2158206848993703</v>
+        <v>0.218752076018325</v>
       </c>
       <c r="T43">
-        <v>2.215939484829352</v>
+        <v>2.254145338016066</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.08419531038256085</v>
+        <v>0.08219066013535703</v>
       </c>
       <c r="W43">
-        <v>0.2159467458117922</v>
+        <v>0.2164194423400828</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2476332658310613</v>
+        <v>0.2417372356922265</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2177723698734633</v>
+        <v>0.2196723698734633</v>
       </c>
       <c r="C44">
-        <v>9.629821095135501</v>
+        <v>9.026359895646692</v>
       </c>
       <c r="D44">
-        <v>19.6751410951355</v>
+        <v>19.46013989564669</v>
       </c>
       <c r="E44">
-        <v>16.26932</v>
+        <v>16.65778</v>
       </c>
       <c r="F44">
-        <v>16.31532</v>
+        <v>16.70378</v>
       </c>
       <c r="G44">
         <v>6.27</v>
@@ -5008,37 +5008,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M44">
-        <v>3.847152455999999</v>
+        <v>3.938751324</v>
       </c>
       <c r="N44">
-        <v>-2.917152455999999</v>
+        <v>-3.008751323999999</v>
       </c>
       <c r="O44">
-        <v>-0.9918318350399998</v>
+        <v>-1.02297545016</v>
       </c>
       <c r="P44">
-        <v>-1.92532062096</v>
+        <v>-1.98577587384</v>
       </c>
       <c r="Q44">
-        <v>-0.02532062095999965</v>
+        <v>-0.08577587383999963</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.218752076018325</v>
+        <v>0.2217863229660149</v>
       </c>
       <c r="T44">
-        <v>2.254145338016065</v>
+        <v>2.293691747454944</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.08219066013535704</v>
+        <v>0.08027924943453478</v>
       </c>
       <c r="W44">
-        <v>0.2164194423400828</v>
+        <v>0.2168701529833367</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2417372356922266</v>
+        <v>0.2361154395133376</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5054,22 +5054,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2196723698734633</v>
+        <v>0.2215723698734633</v>
       </c>
       <c r="C45">
-        <v>9.026359895646692</v>
+        <v>8.42754677912248</v>
       </c>
       <c r="D45">
-        <v>19.46013989564669</v>
+        <v>19.24978677912248</v>
       </c>
       <c r="E45">
-        <v>16.65778</v>
+        <v>17.04624</v>
       </c>
       <c r="F45">
-        <v>16.70378</v>
+        <v>17.09224</v>
       </c>
       <c r="G45">
         <v>6.27</v>
@@ -5090,37 +5090,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M45">
-        <v>3.938751324</v>
+        <v>4.030350192</v>
       </c>
       <c r="N45">
-        <v>-3.008751323999999</v>
+        <v>-3.100350192</v>
       </c>
       <c r="O45">
-        <v>-1.02297545016</v>
+        <v>-1.05411906528</v>
       </c>
       <c r="P45">
-        <v>-1.98577587384</v>
+        <v>-2.04623112672</v>
       </c>
       <c r="Q45">
-        <v>-0.08577587383999963</v>
+        <v>-0.14623112672</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2217863229660149</v>
+        <v>0.2249289358761223</v>
       </c>
       <c r="T45">
-        <v>2.293691747454944</v>
+        <v>2.334650528659497</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.08027924943453478</v>
+        <v>0.07845472103829534</v>
       </c>
       <c r="W45">
-        <v>0.2168701529833367</v>
+        <v>0.21730037677917</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2361154395133376</v>
+        <v>0.230749179524398</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5136,22 +5136,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2215723698734633</v>
+        <v>0.2234723698734633</v>
       </c>
       <c r="C46">
-        <v>8.42754677912248</v>
+        <v>7.833232627988121</v>
       </c>
       <c r="D46">
-        <v>19.24978677912248</v>
+        <v>19.04393262798812</v>
       </c>
       <c r="E46">
-        <v>17.04624</v>
+        <v>17.4347</v>
       </c>
       <c r="F46">
-        <v>17.09224</v>
+        <v>17.4807</v>
       </c>
       <c r="G46">
         <v>6.27</v>
@@ -5172,37 +5172,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M46">
-        <v>4.030350192</v>
+        <v>4.121949059999999</v>
       </c>
       <c r="N46">
-        <v>-3.100350192</v>
+        <v>-3.191949059999999</v>
       </c>
       <c r="O46">
-        <v>-1.05411906528</v>
+        <v>-1.0852626804</v>
       </c>
       <c r="P46">
-        <v>-2.04623112672</v>
+        <v>-2.106686379599999</v>
       </c>
       <c r="Q46">
-        <v>-0.14623112672</v>
+        <v>-0.2066863795999994</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2249289358761223</v>
+        <v>0.2281858256193245</v>
       </c>
       <c r="T46">
-        <v>2.334650528659497</v>
+        <v>2.377098720089668</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.07845472103829534</v>
+        <v>0.07671128279299991</v>
       </c>
       <c r="W46">
-        <v>0.21730037677917</v>
+        <v>0.2177114795174106</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.230749179524398</v>
+        <v>0.2256214199794114</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5218,22 +5218,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2234723698734633</v>
+        <v>0.2253723698734633</v>
       </c>
       <c r="C47">
-        <v>7.833232627988121</v>
+        <v>7.243274635737556</v>
       </c>
       <c r="D47">
-        <v>19.04393262798812</v>
+        <v>18.84243463573756</v>
       </c>
       <c r="E47">
-        <v>17.4347</v>
+        <v>17.82316</v>
       </c>
       <c r="F47">
-        <v>17.4807</v>
+        <v>17.86916</v>
       </c>
       <c r="G47">
         <v>6.27</v>
@@ -5254,37 +5254,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M47">
-        <v>4.121949059999999</v>
+        <v>4.213547928000001</v>
       </c>
       <c r="N47">
-        <v>-3.191949059999999</v>
+        <v>-3.283547928</v>
       </c>
       <c r="O47">
-        <v>-1.0852626804</v>
+        <v>-1.11640629552</v>
       </c>
       <c r="P47">
-        <v>-2.106686379599999</v>
+        <v>-2.16714163248</v>
       </c>
       <c r="Q47">
-        <v>-0.2066863795999994</v>
+        <v>-0.26714163248</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2281858256193245</v>
+        <v>0.2315633409085713</v>
       </c>
       <c r="T47">
-        <v>2.377098720089668</v>
+        <v>2.421119066757996</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.07671128279299991</v>
+        <v>0.07504364621054337</v>
       </c>
       <c r="W47">
-        <v>0.2177114795174106</v>
+        <v>0.2181047082235539</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2256214199794114</v>
+        <v>0.2207166065015981</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5300,22 +5300,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2253723698734633</v>
+        <v>0.2272723698734633</v>
       </c>
       <c r="C48">
-        <v>7.243274635737556</v>
+        <v>6.657535976551781</v>
       </c>
       <c r="D48">
-        <v>18.84243463573756</v>
+        <v>18.64515597655178</v>
       </c>
       <c r="E48">
-        <v>17.82316</v>
+        <v>18.21162</v>
       </c>
       <c r="F48">
-        <v>17.86916</v>
+        <v>18.25762</v>
       </c>
       <c r="G48">
         <v>6.27</v>
@@ -5336,37 +5336,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M48">
-        <v>4.213547928000001</v>
+        <v>4.305146796</v>
       </c>
       <c r="N48">
-        <v>-3.283547928</v>
+        <v>-3.375146796</v>
       </c>
       <c r="O48">
-        <v>-1.11640629552</v>
+        <v>-1.14754991064</v>
       </c>
       <c r="P48">
-        <v>-2.16714163248</v>
+        <v>-2.22759688536</v>
       </c>
       <c r="Q48">
-        <v>-0.26714163248</v>
+        <v>-0.3275968853599998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2315633409085713</v>
+        <v>0.2350683096049595</v>
       </c>
       <c r="T48">
-        <v>2.421119066757996</v>
+        <v>2.466800558583619</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.07504364621054337</v>
+        <v>0.07344697288691479</v>
       </c>
       <c r="W48">
-        <v>0.2181047082235539</v>
+        <v>0.2184812037932655</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2207166065015981</v>
+        <v>0.2160205084909258</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5382,22 +5382,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2272723698734633</v>
+        <v>0.2291723698734633</v>
       </c>
       <c r="C49">
-        <v>6.657535976551781</v>
+        <v>6.075885495456436</v>
       </c>
       <c r="D49">
-        <v>18.64515597655178</v>
+        <v>18.45196549545644</v>
       </c>
       <c r="E49">
-        <v>18.21162</v>
+        <v>18.60008</v>
       </c>
       <c r="F49">
-        <v>18.25762</v>
+        <v>18.64608</v>
       </c>
       <c r="G49">
         <v>6.27</v>
@@ -5418,37 +5418,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M49">
-        <v>4.305146796</v>
+        <v>4.396745664000001</v>
       </c>
       <c r="N49">
-        <v>-3.375146796</v>
+        <v>-3.466745664000001</v>
       </c>
       <c r="O49">
-        <v>-1.14754991064</v>
+        <v>-1.17869352576</v>
       </c>
       <c r="P49">
-        <v>-2.22759688536</v>
+        <v>-2.28805213824</v>
       </c>
       <c r="Q49">
-        <v>-0.3275968853599998</v>
+        <v>-0.3880521382400004</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2350683096049595</v>
+        <v>0.2387080847896702</v>
       </c>
       <c r="T49">
-        <v>2.466800558583619</v>
+        <v>2.514239030864073</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.07344697288691479</v>
+        <v>0.07191682761843739</v>
       </c>
       <c r="W49">
-        <v>0.2184812037932655</v>
+        <v>0.2188420120475725</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2160205084909258</v>
+        <v>0.2115200812306982</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5464,22 +5464,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2291723698734633</v>
+        <v>0.2310723698734633</v>
       </c>
       <c r="C50">
-        <v>6.07588549545644</v>
+        <v>5.498197417544386</v>
       </c>
       <c r="D50">
-        <v>18.45196549545644</v>
+        <v>18.26273741754438</v>
       </c>
       <c r="E50">
-        <v>18.60008</v>
+        <v>18.98854</v>
       </c>
       <c r="F50">
-        <v>18.64608</v>
+        <v>19.03454</v>
       </c>
       <c r="G50">
         <v>6.27</v>
@@ -5500,37 +5500,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M50">
-        <v>4.396745664</v>
+        <v>4.488344531999999</v>
       </c>
       <c r="N50">
-        <v>-3.466745664</v>
+        <v>-3.558344531999999</v>
       </c>
       <c r="O50">
-        <v>-1.17869352576</v>
+        <v>-1.20983714088</v>
       </c>
       <c r="P50">
-        <v>-2.28805213824</v>
+        <v>-2.348507391119999</v>
       </c>
       <c r="Q50">
-        <v>-0.38805213824</v>
+        <v>-0.4485073911199993</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2387080847896702</v>
+        <v>0.2424905962561343</v>
       </c>
       <c r="T50">
-        <v>2.514239030864073</v>
+        <v>2.563537835390819</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0719168276184374</v>
+        <v>0.07044913725887746</v>
       </c>
       <c r="W50">
-        <v>0.2188420120475725</v>
+        <v>0.2191880934343567</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2115200812306982</v>
+        <v>0.2072033448790513</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5546,22 +5546,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2310723698734633</v>
+        <v>0.2329723698734633</v>
       </c>
       <c r="C51">
-        <v>5.498197417544386</v>
+        <v>4.92435107490849</v>
       </c>
       <c r="D51">
-        <v>18.26273741754438</v>
+        <v>18.07735107490849</v>
       </c>
       <c r="E51">
-        <v>18.98854</v>
+        <v>19.377</v>
       </c>
       <c r="F51">
-        <v>19.03454</v>
+        <v>19.423</v>
       </c>
       <c r="G51">
         <v>6.27</v>
@@ -5582,37 +5582,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M51">
-        <v>4.488344531999999</v>
+        <v>4.579943399999999</v>
       </c>
       <c r="N51">
-        <v>-3.558344531999999</v>
+        <v>-3.649943399999999</v>
       </c>
       <c r="O51">
-        <v>-1.20983714088</v>
+        <v>-1.240980756</v>
       </c>
       <c r="P51">
-        <v>-2.348507391119999</v>
+        <v>-2.408962643999999</v>
       </c>
       <c r="Q51">
-        <v>-0.4485073911199993</v>
+        <v>-0.5089626439999995</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2424905962561343</v>
+        <v>0.246424408181257</v>
       </c>
       <c r="T51">
-        <v>2.563537835390819</v>
+        <v>2.614808592098636</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07044913725887746</v>
+        <v>0.06904015451369991</v>
       </c>
       <c r="W51">
-        <v>0.2191880934343567</v>
+        <v>0.2195203315656696</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2072033448790513</v>
+        <v>0.2030592779814703</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5628,22 +5628,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2329723698734633</v>
+        <v>0.2348723698734632</v>
       </c>
       <c r="C52">
-        <v>4.92435107490849</v>
+        <v>4.354230650038833</v>
       </c>
       <c r="D52">
-        <v>18.07735107490849</v>
+        <v>17.89569065003883</v>
       </c>
       <c r="E52">
-        <v>19.377</v>
+        <v>19.76546</v>
       </c>
       <c r="F52">
-        <v>19.423</v>
+        <v>19.81146</v>
       </c>
       <c r="G52">
         <v>6.27</v>
@@ -5664,37 +5664,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M52">
-        <v>4.579943399999999</v>
+        <v>4.671542268</v>
       </c>
       <c r="N52">
-        <v>-3.649943399999999</v>
+        <v>-3.741542268</v>
       </c>
       <c r="O52">
-        <v>-1.240980756</v>
+        <v>-1.27212437112</v>
       </c>
       <c r="P52">
-        <v>-2.408962643999999</v>
+        <v>-2.46941789688</v>
       </c>
       <c r="Q52">
-        <v>-0.5089626439999995</v>
+        <v>-0.5694178968800006</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.246424408181257</v>
+        <v>0.2505187838584255</v>
       </c>
       <c r="T52">
-        <v>2.614808592098636</v>
+        <v>2.66817203275371</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06904015451369991</v>
+        <v>0.06768642599382343</v>
       </c>
       <c r="W52">
-        <v>0.2195203315656696</v>
+        <v>0.2198395407506564</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2030592779814703</v>
+        <v>0.1990777235112453</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5710,22 +5710,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2348723698734632</v>
+        <v>0.2367723698734633</v>
       </c>
       <c r="C53">
-        <v>4.354230650038833</v>
+        <v>3.787724934537668</v>
       </c>
       <c r="D53">
-        <v>17.89569065003883</v>
+        <v>17.71764493453767</v>
       </c>
       <c r="E53">
-        <v>19.76546</v>
+        <v>20.15392</v>
       </c>
       <c r="F53">
-        <v>19.81146</v>
+        <v>20.19992</v>
       </c>
       <c r="G53">
         <v>6.27</v>
@@ -5746,37 +5746,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M53">
-        <v>4.671542268</v>
+        <v>4.763141136</v>
       </c>
       <c r="N53">
-        <v>-3.741542268</v>
+        <v>-3.833141136</v>
       </c>
       <c r="O53">
-        <v>-1.27212437112</v>
+        <v>-1.30326798624</v>
       </c>
       <c r="P53">
-        <v>-2.46941789688</v>
+        <v>-2.529873149759999</v>
       </c>
       <c r="Q53">
-        <v>-0.5694178968800006</v>
+        <v>-0.6298731497599994</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2505187838584255</v>
+        <v>0.2547837585221427</v>
       </c>
       <c r="T53">
-        <v>2.66817203275371</v>
+        <v>2.723758950102746</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06768642599382343</v>
+        <v>0.06638476395548068</v>
       </c>
       <c r="W53">
-        <v>0.2198395407506564</v>
+        <v>0.2201464726592977</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1990777235112453</v>
+        <v>0.1952493057514137</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5792,22 +5792,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2367723698734633</v>
+        <v>0.2386723698734633</v>
       </c>
       <c r="C54">
-        <v>3.787724934537668</v>
+        <v>3.224727102095894</v>
       </c>
       <c r="D54">
-        <v>17.71764493453767</v>
+        <v>17.5431071020959</v>
       </c>
       <c r="E54">
-        <v>20.15392</v>
+        <v>20.54238</v>
       </c>
       <c r="F54">
-        <v>20.19992</v>
+        <v>20.58838</v>
       </c>
       <c r="G54">
         <v>6.27</v>
@@ -5828,37 +5828,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M54">
-        <v>4.763141136</v>
+        <v>4.854740004</v>
       </c>
       <c r="N54">
-        <v>-3.833141136</v>
+        <v>-3.924740004</v>
       </c>
       <c r="O54">
-        <v>-1.30326798624</v>
+        <v>-1.33441160136</v>
       </c>
       <c r="P54">
-        <v>-2.529873149759999</v>
+        <v>-2.59032840264</v>
       </c>
       <c r="Q54">
-        <v>-0.6298731497599994</v>
+        <v>-0.6903284026400001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2547837585221427</v>
+        <v>0.2592302214694224</v>
       </c>
       <c r="T54">
-        <v>2.723758950102746</v>
+        <v>2.781711268190038</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06638476395548068</v>
+        <v>0.06513222123933954</v>
       </c>
       <c r="W54">
-        <v>0.2201464726592977</v>
+        <v>0.2204418222317638</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1952493057514137</v>
+        <v>0.1915653565862927</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5874,22 +5874,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2386723698734633</v>
+        <v>0.2405723698734633</v>
       </c>
       <c r="C55">
-        <v>3.224727102095894</v>
+        <v>2.665134494757201</v>
       </c>
       <c r="D55">
-        <v>17.5431071020959</v>
+        <v>17.3719744947572</v>
       </c>
       <c r="E55">
-        <v>20.54238</v>
+        <v>20.93084</v>
       </c>
       <c r="F55">
-        <v>20.58838</v>
+        <v>20.97684</v>
       </c>
       <c r="G55">
         <v>6.27</v>
@@ -5910,37 +5910,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M55">
-        <v>4.854740004</v>
+        <v>4.946338872</v>
       </c>
       <c r="N55">
-        <v>-3.924740004</v>
+        <v>-4.016338872</v>
       </c>
       <c r="O55">
-        <v>-1.33441160136</v>
+        <v>-1.36555521648</v>
       </c>
       <c r="P55">
-        <v>-2.59032840264</v>
+        <v>-2.65078365552</v>
       </c>
       <c r="Q55">
-        <v>-0.6903284026400001</v>
+        <v>-0.7507836555200003</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2592302214694224</v>
+        <v>0.2638700088926707</v>
       </c>
       <c r="T55">
-        <v>2.781711268190038</v>
+        <v>2.842183252281127</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06513222123933954</v>
+        <v>0.06392606899416657</v>
       </c>
       <c r="W55">
-        <v>0.2204418222317638</v>
+        <v>0.2207262329311755</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1915653565862927</v>
+        <v>0.1880178499828428</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5956,22 +5956,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2405723698734633</v>
+        <v>0.2424723698734633</v>
       </c>
       <c r="C56">
-        <v>2.665134494757201</v>
+        <v>2.108848421571246</v>
       </c>
       <c r="D56">
-        <v>17.3719744947572</v>
+        <v>17.20414842157125</v>
       </c>
       <c r="E56">
-        <v>20.93084</v>
+        <v>21.3193</v>
       </c>
       <c r="F56">
-        <v>20.97684</v>
+        <v>21.3653</v>
       </c>
       <c r="G56">
         <v>6.27</v>
@@ -5992,37 +5992,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M56">
-        <v>4.946338872</v>
+        <v>5.03793774</v>
       </c>
       <c r="N56">
-        <v>-4.016338872</v>
+        <v>-4.107937740000001</v>
       </c>
       <c r="O56">
-        <v>-1.36555521648</v>
+        <v>-1.3966988316</v>
       </c>
       <c r="P56">
-        <v>-2.65078365552</v>
+        <v>-2.7112389084</v>
       </c>
       <c r="Q56">
-        <v>-0.7507836555200003</v>
+        <v>-0.8112389084000005</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2638700088926707</v>
+        <v>0.2687160090902856</v>
       </c>
       <c r="T56">
-        <v>2.842183252281127</v>
+        <v>2.905342880109596</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06392606899416657</v>
+        <v>0.06276377683063628</v>
       </c>
       <c r="W56">
-        <v>0.2207262329311755</v>
+        <v>0.221000301423336</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1880178499828428</v>
+        <v>0.1845993436195184</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6038,22 +6038,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2424723698734633</v>
+        <v>0.2443723698734633</v>
       </c>
       <c r="C57">
-        <v>2.108848421571246</v>
+        <v>1.555773968806168</v>
       </c>
       <c r="D57">
-        <v>17.20414842157125</v>
+        <v>17.03953396880617</v>
       </c>
       <c r="E57">
-        <v>21.3193</v>
+        <v>21.70776</v>
       </c>
       <c r="F57">
-        <v>21.3653</v>
+        <v>21.75376</v>
       </c>
       <c r="G57">
         <v>6.27</v>
@@ -6074,37 +6074,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M57">
-        <v>5.03793774</v>
+        <v>5.129536608</v>
       </c>
       <c r="N57">
-        <v>-4.107937740000001</v>
+        <v>-4.199536608000001</v>
       </c>
       <c r="O57">
-        <v>-1.3966988316</v>
+        <v>-1.42784244672</v>
       </c>
       <c r="P57">
-        <v>-2.7112389084</v>
+        <v>-2.77169416128</v>
       </c>
       <c r="Q57">
-        <v>-0.8112389084000005</v>
+        <v>-0.8716941612800002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2687160090902856</v>
+        <v>0.2737822820241557</v>
       </c>
       <c r="T57">
-        <v>2.905342880109596</v>
+        <v>2.971373400112087</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06276377683063628</v>
+        <v>0.06164299510151776</v>
       </c>
       <c r="W57">
-        <v>0.221000301423336</v>
+        <v>0.2212645817550621</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1845993436195184</v>
+        <v>0.1813029267691698</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2443723698734633</v>
+        <v>0.2462723698734633</v>
       </c>
       <c r="C58">
-        <v>1.555773968806168</v>
+        <v>1.005819820953441</v>
       </c>
       <c r="D58">
-        <v>17.03953396880617</v>
+        <v>16.87803982095344</v>
       </c>
       <c r="E58">
-        <v>21.70776</v>
+        <v>22.09622</v>
       </c>
       <c r="F58">
-        <v>21.75376</v>
+        <v>22.14222</v>
       </c>
       <c r="G58">
         <v>6.27</v>
@@ -6156,37 +6156,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M58">
-        <v>5.129536608</v>
+        <v>5.221135476000001</v>
       </c>
       <c r="N58">
-        <v>-4.199536608000001</v>
+        <v>-4.291135476000001</v>
       </c>
       <c r="O58">
-        <v>-1.42784244672</v>
+        <v>-1.45898606184</v>
       </c>
       <c r="P58">
-        <v>-2.77169416128</v>
+        <v>-2.832149414160001</v>
       </c>
       <c r="Q58">
-        <v>-0.8716941612800002</v>
+        <v>-0.9321494141600009</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2737822820241557</v>
+        <v>0.2790841955596012</v>
       </c>
       <c r="T58">
-        <v>2.971373400112087</v>
+        <v>3.040475107091437</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06164299510151776</v>
+        <v>0.06056153904710517</v>
       </c>
       <c r="W58">
-        <v>0.2212645817550621</v>
+        <v>0.2215195890926926</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1813029267691698</v>
+        <v>0.1781221736679562</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6202,22 +6202,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2462723698734633</v>
+        <v>0.2481723698734633</v>
       </c>
       <c r="C59">
-        <v>1.005819820953441</v>
+        <v>0.4588980918158967</v>
       </c>
       <c r="D59">
-        <v>16.87803982095344</v>
+        <v>16.7195780918159</v>
       </c>
       <c r="E59">
-        <v>22.09622</v>
+        <v>22.48468</v>
       </c>
       <c r="F59">
-        <v>22.14222</v>
+        <v>22.53068</v>
       </c>
       <c r="G59">
         <v>6.27</v>
@@ -6238,37 +6238,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M59">
-        <v>5.221135476000001</v>
+        <v>5.312734344</v>
       </c>
       <c r="N59">
-        <v>-4.291135476000001</v>
+        <v>-4.382734343999999</v>
       </c>
       <c r="O59">
-        <v>-1.45898606184</v>
+        <v>-1.49012967696</v>
       </c>
       <c r="P59">
-        <v>-2.832149414160001</v>
+        <v>-2.89260466704</v>
       </c>
       <c r="Q59">
-        <v>-0.9321494141600009</v>
+        <v>-0.9926046670399997</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2790841955596012</v>
+        <v>0.2846385811681632</v>
       </c>
       <c r="T59">
-        <v>3.040475107091437</v>
+        <v>3.112867371545996</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06056153904710517</v>
+        <v>0.05951737458077578</v>
       </c>
       <c r="W59">
-        <v>0.2215195890926926</v>
+        <v>0.2217658030738531</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1781221736679562</v>
+        <v>0.1750511017081642</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6284,22 +6284,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2481723698734633</v>
+        <v>0.2500723698734633</v>
       </c>
       <c r="C60">
-        <v>0.4588980918159002</v>
+        <v>-0.08507583497766191</v>
       </c>
       <c r="D60">
-        <v>16.7195780918159</v>
+        <v>16.56406416502233</v>
       </c>
       <c r="E60">
-        <v>22.48468</v>
+        <v>22.87314</v>
       </c>
       <c r="F60">
-        <v>22.53068</v>
+        <v>22.91914</v>
       </c>
       <c r="G60">
         <v>6.27</v>
@@ -6320,37 +6320,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M60">
-        <v>5.312734343999999</v>
+        <v>5.404333211999999</v>
       </c>
       <c r="N60">
-        <v>-4.382734343999999</v>
+        <v>-4.474333211999999</v>
       </c>
       <c r="O60">
-        <v>-1.49012967696</v>
+        <v>-1.52127329208</v>
       </c>
       <c r="P60">
-        <v>-2.89260466704</v>
+        <v>-2.953059919919999</v>
       </c>
       <c r="Q60">
-        <v>-0.9926046670399997</v>
+        <v>-1.053059919919999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2846385811681631</v>
+        <v>0.290463912416167</v>
       </c>
       <c r="T60">
-        <v>3.112867371545995</v>
+        <v>3.188790965973946</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05951737458077579</v>
+        <v>0.05850860552008467</v>
       </c>
       <c r="W60">
-        <v>0.2217658030738531</v>
+        <v>0.2220036708183641</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.175051101708164</v>
+        <v>0.1720841338826019</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6366,22 +6366,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2500723698734633</v>
+        <v>0.2519723698734633</v>
       </c>
       <c r="C61">
-        <v>-0.08507583497766191</v>
+        <v>-0.6261834566393745</v>
       </c>
       <c r="D61">
-        <v>16.56406416502233</v>
+        <v>16.41141654336062</v>
       </c>
       <c r="E61">
-        <v>22.87314</v>
+        <v>23.2616</v>
       </c>
       <c r="F61">
-        <v>22.91914</v>
+        <v>23.3076</v>
       </c>
       <c r="G61">
         <v>6.27</v>
@@ -6402,37 +6402,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M61">
-        <v>5.404333211999999</v>
+        <v>5.495932079999999</v>
       </c>
       <c r="N61">
-        <v>-4.474333211999999</v>
+        <v>-4.56593208</v>
       </c>
       <c r="O61">
-        <v>-1.52127329208</v>
+        <v>-1.5524169072</v>
       </c>
       <c r="P61">
-        <v>-2.953059919919999</v>
+        <v>-3.0135151728</v>
       </c>
       <c r="Q61">
-        <v>-1.053059919919999</v>
+        <v>-1.1135151728</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.290463912416167</v>
+        <v>0.2965805102265713</v>
       </c>
       <c r="T61">
-        <v>3.188790965973946</v>
+        <v>3.268510740123295</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05850860552008467</v>
+        <v>0.05753346209474993</v>
       </c>
       <c r="W61">
-        <v>0.2220036708183641</v>
+        <v>0.222233609638058</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1720841338826019</v>
+        <v>0.1692160649845585</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6448,22 +6448,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2519723698734633</v>
+        <v>0.2538723698734633</v>
       </c>
       <c r="C62">
-        <v>-0.6261834566393745</v>
+        <v>-1.164503293634301</v>
       </c>
       <c r="D62">
-        <v>16.41141654336062</v>
+        <v>16.2615567063657</v>
       </c>
       <c r="E62">
-        <v>23.2616</v>
+        <v>23.65006</v>
       </c>
       <c r="F62">
-        <v>23.3076</v>
+        <v>23.69606</v>
       </c>
       <c r="G62">
         <v>6.27</v>
@@ -6484,37 +6484,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M62">
-        <v>5.495932079999999</v>
+        <v>5.587530947999999</v>
       </c>
       <c r="N62">
-        <v>-4.56593208</v>
+        <v>-4.657530948</v>
       </c>
       <c r="O62">
-        <v>-1.5524169072</v>
+        <v>-1.58356052232</v>
       </c>
       <c r="P62">
-        <v>-3.0135151728</v>
+        <v>-3.07397042568</v>
       </c>
       <c r="Q62">
-        <v>-1.1135151728</v>
+        <v>-1.17397042568</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2965805102265713</v>
+        <v>0.3030107797195603</v>
       </c>
       <c r="T62">
-        <v>3.268510740123295</v>
+        <v>3.352318707818764</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05753346209474993</v>
+        <v>0.05659029058499992</v>
       </c>
       <c r="W62">
-        <v>0.222233609638058</v>
+        <v>0.222456009480057</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1692160649845585</v>
+        <v>0.1664420311323527</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6530,22 +6530,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2538723698734633</v>
+        <v>0.2557723698734633</v>
       </c>
       <c r="C63">
-        <v>-1.164503293634301</v>
+        <v>-1.700111024360563</v>
       </c>
       <c r="D63">
-        <v>16.2615567063657</v>
+        <v>16.11440897563944</v>
       </c>
       <c r="E63">
-        <v>23.65006</v>
+        <v>24.03852</v>
       </c>
       <c r="F63">
-        <v>23.69606</v>
+        <v>24.08452</v>
       </c>
       <c r="G63">
         <v>6.27</v>
@@ -6566,37 +6566,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M63">
-        <v>5.587530947999999</v>
+        <v>5.679129816</v>
       </c>
       <c r="N63">
-        <v>-4.657530948</v>
+        <v>-4.749129816</v>
       </c>
       <c r="O63">
-        <v>-1.58356052232</v>
+        <v>-1.61470413744</v>
       </c>
       <c r="P63">
-        <v>-3.07397042568</v>
+        <v>-3.13442567856</v>
       </c>
       <c r="Q63">
-        <v>-1.17397042568</v>
+        <v>-1.23442567856</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3030107797195603</v>
+        <v>0.3097794844490224</v>
       </c>
       <c r="T63">
-        <v>3.352318707818764</v>
+        <v>3.440537621182415</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05659029058499992</v>
+        <v>0.05567754396266121</v>
       </c>
       <c r="W63">
-        <v>0.222456009480057</v>
+        <v>0.2226712351336045</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1664420311323527</v>
+        <v>0.1637574822431211</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6612,22 +6612,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2557723698734633</v>
+        <v>0.2576723698734633</v>
       </c>
       <c r="C64">
-        <v>-1.700111024360563</v>
+        <v>-2.233079612582806</v>
       </c>
       <c r="D64">
-        <v>16.11440897563944</v>
+        <v>15.9699003874172</v>
       </c>
       <c r="E64">
-        <v>24.03852</v>
+        <v>24.42698</v>
       </c>
       <c r="F64">
-        <v>24.08452</v>
+        <v>24.47298</v>
       </c>
       <c r="G64">
         <v>6.27</v>
@@ -6648,37 +6648,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M64">
-        <v>5.679129816</v>
+        <v>5.770728684</v>
       </c>
       <c r="N64">
-        <v>-4.749129816</v>
+        <v>-4.840728684</v>
       </c>
       <c r="O64">
-        <v>-1.61470413744</v>
+        <v>-1.64584775256</v>
       </c>
       <c r="P64">
-        <v>-3.13442567856</v>
+        <v>-3.19488093144</v>
       </c>
       <c r="Q64">
-        <v>-1.23442567856</v>
+        <v>-1.29488093144</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3097794844490224</v>
+        <v>0.3169140651098067</v>
       </c>
       <c r="T64">
-        <v>3.440537621182415</v>
+        <v>3.533525124457616</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05567754396266121</v>
+        <v>0.05479377342357135</v>
       </c>
       <c r="W64">
-        <v>0.2226712351336045</v>
+        <v>0.2228796282267219</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1637574822431211</v>
+        <v>0.161158157128151</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6694,22 +6694,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2576723698734633</v>
+        <v>0.2595723698734633</v>
       </c>
       <c r="C65">
-        <v>-2.233079612582806</v>
+        <v>-2.763479428069964</v>
       </c>
       <c r="D65">
-        <v>15.9699003874172</v>
+        <v>15.82796057193003</v>
       </c>
       <c r="E65">
-        <v>24.42698</v>
+        <v>24.81544</v>
       </c>
       <c r="F65">
-        <v>24.47298</v>
+        <v>24.86144</v>
       </c>
       <c r="G65">
         <v>6.27</v>
@@ -6730,37 +6730,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M65">
-        <v>5.770728684</v>
+        <v>5.862327552</v>
       </c>
       <c r="N65">
-        <v>-4.840728684</v>
+        <v>-4.932327552</v>
       </c>
       <c r="O65">
-        <v>-1.64584775256</v>
+        <v>-1.67699136768</v>
       </c>
       <c r="P65">
-        <v>-3.19488093144</v>
+        <v>-3.25533618432</v>
       </c>
       <c r="Q65">
-        <v>-1.29488093144</v>
+        <v>-1.35533618432</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3169140651098067</v>
+        <v>0.3244450113628569</v>
       </c>
       <c r="T65">
-        <v>3.533525124457616</v>
+        <v>3.631678600136994</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05479377342357135</v>
+        <v>0.05393762071382804</v>
       </c>
       <c r="W65">
-        <v>0.2228796282267219</v>
+        <v>0.2230815090356794</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.161158157128151</v>
+        <v>0.1586400609230236</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6776,22 +6776,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2595723698734633</v>
+        <v>0.2614723698734633</v>
       </c>
       <c r="C66">
-        <v>-2.763479428069964</v>
+        <v>-3.29137836085636</v>
       </c>
       <c r="D66">
-        <v>15.82796057193003</v>
+        <v>15.68852163914364</v>
       </c>
       <c r="E66">
-        <v>24.81544</v>
+        <v>25.2039</v>
       </c>
       <c r="F66">
-        <v>24.86144</v>
+        <v>25.2499</v>
       </c>
       <c r="G66">
         <v>6.27</v>
@@ -6812,37 +6812,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M66">
-        <v>5.862327552</v>
+        <v>5.95392642</v>
       </c>
       <c r="N66">
-        <v>-4.932327552</v>
+        <v>-5.02392642</v>
       </c>
       <c r="O66">
-        <v>-1.67699136768</v>
+        <v>-1.7081349828</v>
       </c>
       <c r="P66">
-        <v>-3.25533618432</v>
+        <v>-3.3157914372</v>
       </c>
       <c r="Q66">
-        <v>-1.35533618432</v>
+        <v>-1.4157914372</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3244450113628569</v>
+        <v>0.3324062974017958</v>
       </c>
       <c r="T66">
-        <v>3.631678600136994</v>
+        <v>3.735440845855194</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05393762071382804</v>
+        <v>0.05310781116438455</v>
       </c>
       <c r="W66">
-        <v>0.2230815090356794</v>
+        <v>0.2232771781274381</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1586400609230236</v>
+        <v>0.1561994446011309</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6858,22 +6858,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2614723698734633</v>
+        <v>0.2633723698734633</v>
       </c>
       <c r="C67">
-        <v>-3.29137836085636</v>
+        <v>-3.816841929515874</v>
       </c>
       <c r="D67">
-        <v>15.68852163914364</v>
+        <v>15.55151807048413</v>
       </c>
       <c r="E67">
-        <v>25.2039</v>
+        <v>25.59236</v>
       </c>
       <c r="F67">
-        <v>25.2499</v>
+        <v>25.63836</v>
       </c>
       <c r="G67">
         <v>6.27</v>
@@ -6894,37 +6894,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M67">
-        <v>5.95392642</v>
+        <v>6.045525288</v>
       </c>
       <c r="N67">
-        <v>-5.02392642</v>
+        <v>-5.115525288000001</v>
       </c>
       <c r="O67">
-        <v>-1.7081349828</v>
+        <v>-1.73927859792</v>
       </c>
       <c r="P67">
-        <v>-3.3157914372</v>
+        <v>-3.37624669008</v>
       </c>
       <c r="Q67">
-        <v>-1.4157914372</v>
+        <v>-1.47624669008</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3324062974017958</v>
+        <v>0.3408358943842015</v>
       </c>
       <c r="T67">
-        <v>3.735440845855194</v>
+        <v>3.845306753086229</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05310781116438455</v>
+        <v>0.05230314735886356</v>
       </c>
       <c r="W67">
-        <v>0.2232771781274381</v>
+        <v>0.22346691785278</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1561994446011309</v>
+        <v>0.1538327863495986</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6940,22 +6940,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2633723698734633</v>
+        <v>0.2652723698734633</v>
       </c>
       <c r="C68">
-        <v>-3.816841929515874</v>
+        <v>-4.339933383812177</v>
       </c>
       <c r="D68">
-        <v>15.55151807048413</v>
+        <v>15.41688661618782</v>
       </c>
       <c r="E68">
-        <v>25.59236</v>
+        <v>25.98082</v>
       </c>
       <c r="F68">
-        <v>25.63836</v>
+        <v>26.02682</v>
       </c>
       <c r="G68">
         <v>6.27</v>
@@ -6976,37 +6976,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M68">
-        <v>6.045525288</v>
+        <v>6.137124156</v>
       </c>
       <c r="N68">
-        <v>-5.115525288000001</v>
+        <v>-5.207124156000001</v>
       </c>
       <c r="O68">
-        <v>-1.73927859792</v>
+        <v>-1.77042221304</v>
       </c>
       <c r="P68">
-        <v>-3.37624669008</v>
+        <v>-3.43670194296</v>
       </c>
       <c r="Q68">
-        <v>-1.47624669008</v>
+        <v>-1.53670194296</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3408358943842015</v>
+        <v>0.3497763760322076</v>
       </c>
       <c r="T68">
-        <v>3.845306753086229</v>
+        <v>3.961831200149449</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05230314735886356</v>
+        <v>0.05152250336843276</v>
       </c>
       <c r="W68">
-        <v>0.22346691785278</v>
+        <v>0.2236509937057236</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1538327863495986</v>
+        <v>0.1515367746130375</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7022,22 +7022,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2652723698734633</v>
+        <v>0.2671723698734633</v>
       </c>
       <c r="C69">
-        <v>-4.339933383812177</v>
+        <v>-4.860713802062659</v>
       </c>
       <c r="D69">
-        <v>15.41688661618782</v>
+        <v>15.28456619793734</v>
       </c>
       <c r="E69">
-        <v>25.98082</v>
+        <v>26.36928</v>
       </c>
       <c r="F69">
-        <v>26.02682</v>
+        <v>26.41528</v>
       </c>
       <c r="G69">
         <v>6.27</v>
@@ -7058,37 +7058,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M69">
-        <v>6.137124156</v>
+        <v>6.228723024</v>
       </c>
       <c r="N69">
-        <v>-5.207124156000001</v>
+        <v>-5.298723023999999</v>
       </c>
       <c r="O69">
-        <v>-1.77042221304</v>
+        <v>-1.80156582816</v>
       </c>
       <c r="P69">
-        <v>-3.43670194296</v>
+        <v>-3.497157195839999</v>
       </c>
       <c r="Q69">
-        <v>-1.53670194296</v>
+        <v>-1.597157195839999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3497763760322076</v>
+        <v>0.3592756377832141</v>
       </c>
       <c r="T69">
-        <v>3.961831200149449</v>
+        <v>4.085638425154119</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05152250336843276</v>
+        <v>0.05076481949536758</v>
       </c>
       <c r="W69">
-        <v>0.2236509937057236</v>
+        <v>0.2238296555629923</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1515367746130375</v>
+        <v>0.1493082926334341</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7104,22 +7104,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2671723698734633</v>
+        <v>0.2690723698734633</v>
       </c>
       <c r="C70">
-        <v>-4.860713802062659</v>
+        <v>-5.379242183531172</v>
       </c>
       <c r="D70">
-        <v>15.28456619793734</v>
+        <v>15.15449781646883</v>
       </c>
       <c r="E70">
-        <v>26.36928</v>
+        <v>26.75774</v>
       </c>
       <c r="F70">
-        <v>26.41528</v>
+        <v>26.80374</v>
       </c>
       <c r="G70">
         <v>6.27</v>
@@ -7140,37 +7140,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M70">
-        <v>6.228723024</v>
+        <v>6.320321892000001</v>
       </c>
       <c r="N70">
-        <v>-5.298723023999999</v>
+        <v>-5.390321892000001</v>
       </c>
       <c r="O70">
-        <v>-1.80156582816</v>
+        <v>-1.83270944328</v>
       </c>
       <c r="P70">
-        <v>-3.497157195839999</v>
+        <v>-3.55761244872</v>
       </c>
       <c r="Q70">
-        <v>-1.597157195839999</v>
+        <v>-1.657612448720001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3592756377832141</v>
+        <v>0.3693877551310598</v>
       </c>
       <c r="T70">
-        <v>4.085638425154119</v>
+        <v>4.217433213062317</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05076481949536758</v>
+        <v>0.05002909747369558</v>
       </c>
       <c r="W70">
-        <v>0.2238296555629923</v>
+        <v>0.2240031388157026</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1493082926334341</v>
+        <v>0.1471444043343987</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7186,22 +7186,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2690723698734633</v>
+        <v>0.2709723698734633</v>
       </c>
       <c r="C71">
-        <v>-5.379242183531172</v>
+        <v>-5.895575536143092</v>
       </c>
       <c r="D71">
-        <v>15.15449781646883</v>
+        <v>15.02662446385691</v>
       </c>
       <c r="E71">
-        <v>26.75774</v>
+        <v>27.1462</v>
       </c>
       <c r="F71">
-        <v>26.80374</v>
+        <v>27.1922</v>
       </c>
       <c r="G71">
         <v>6.27</v>
@@ -7222,37 +7222,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M71">
-        <v>6.320321892000001</v>
+        <v>6.41192076</v>
       </c>
       <c r="N71">
-        <v>-5.390321892000001</v>
+        <v>-5.48192076</v>
       </c>
       <c r="O71">
-        <v>-1.83270944328</v>
+        <v>-1.8638530584</v>
       </c>
       <c r="P71">
-        <v>-3.55761244872</v>
+        <v>-3.618067701599999</v>
       </c>
       <c r="Q71">
-        <v>-1.657612448720001</v>
+        <v>-1.718067701599999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3693877551310598</v>
+        <v>0.3801740136354285</v>
       </c>
       <c r="T71">
-        <v>4.217433213062317</v>
+        <v>4.358014320164394</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05002909747369558</v>
+        <v>0.04931439608121422</v>
       </c>
       <c r="W71">
-        <v>0.2240031388157026</v>
+        <v>0.2241716654040497</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1471444043343987</v>
+        <v>0.145042341415336</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7268,22 +7268,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2709723698734633</v>
+        <v>0.2728723698734633</v>
       </c>
       <c r="C72">
-        <v>-5.895575536143092</v>
+        <v>-6.409768959796697</v>
       </c>
       <c r="D72">
-        <v>15.02662446385691</v>
+        <v>14.90089104020331</v>
       </c>
       <c r="E72">
-        <v>27.1462</v>
+        <v>27.53466</v>
       </c>
       <c r="F72">
-        <v>27.1922</v>
+        <v>27.58066</v>
       </c>
       <c r="G72">
         <v>6.27</v>
@@ -7304,37 +7304,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M72">
-        <v>6.41192076</v>
+        <v>6.503519628</v>
       </c>
       <c r="N72">
-        <v>-5.48192076</v>
+        <v>-5.573519628</v>
       </c>
       <c r="O72">
-        <v>-1.8638530584</v>
+        <v>-1.89499667352</v>
       </c>
       <c r="P72">
-        <v>-3.618067701599999</v>
+        <v>-3.67852295448</v>
       </c>
       <c r="Q72">
-        <v>-1.718067701599999</v>
+        <v>-1.77852295448</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3801740136354285</v>
+        <v>0.3917041520366501</v>
       </c>
       <c r="T72">
-        <v>4.358014320164394</v>
+        <v>4.508290676032132</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04931439608121422</v>
+        <v>0.04861982712232387</v>
       </c>
       <c r="W72">
-        <v>0.2241716654040497</v>
+        <v>0.2243354447645561</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.145042341415336</v>
+        <v>0.1429994915362467</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7350,22 +7350,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2728723698734633</v>
+        <v>0.2747723698734633</v>
       </c>
       <c r="C73">
-        <v>-6.40976895979669</v>
+        <v>-6.921875725526686</v>
       </c>
       <c r="D73">
-        <v>14.90089104020331</v>
+        <v>14.77724427447331</v>
       </c>
       <c r="E73">
-        <v>27.53466</v>
+        <v>27.92312</v>
       </c>
       <c r="F73">
-        <v>27.58065999999999</v>
+        <v>27.96912</v>
       </c>
       <c r="G73">
         <v>6.27</v>
@@ -7386,37 +7386,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M73">
-        <v>6.503519627999999</v>
+        <v>6.595118496</v>
       </c>
       <c r="N73">
-        <v>-5.573519628</v>
+        <v>-5.665118496</v>
       </c>
       <c r="O73">
-        <v>-1.89499667352</v>
+        <v>-1.92614028864</v>
       </c>
       <c r="P73">
-        <v>-3.67852295448</v>
+        <v>-3.73897820736</v>
       </c>
       <c r="Q73">
-        <v>-1.77852295448</v>
+        <v>-1.83897820736</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.39170415203665</v>
+        <v>0.4040578717522446</v>
       </c>
       <c r="T73">
-        <v>4.50829067603213</v>
+        <v>4.669301057318992</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04861982712232388</v>
+        <v>0.04794455174562494</v>
       </c>
       <c r="W73">
-        <v>0.224335444764556</v>
+        <v>0.2244946746983816</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1429994915362466</v>
+        <v>0.1410133874871321</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7432,22 +7432,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2747723698734633</v>
+        <v>0.2766723698734633</v>
       </c>
       <c r="C74">
-        <v>-6.921875725526686</v>
+        <v>-7.431947350758794</v>
       </c>
       <c r="D74">
-        <v>14.77724427447331</v>
+        <v>14.6556326492412</v>
       </c>
       <c r="E74">
-        <v>27.92312</v>
+        <v>28.31158</v>
       </c>
       <c r="F74">
-        <v>27.96912</v>
+        <v>28.35758</v>
       </c>
       <c r="G74">
         <v>6.27</v>
@@ -7468,37 +7468,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M74">
-        <v>6.595118496</v>
+        <v>6.686717363999999</v>
       </c>
       <c r="N74">
-        <v>-5.665118496</v>
+        <v>-5.756717363999998</v>
       </c>
       <c r="O74">
-        <v>-1.92614028864</v>
+        <v>-1.95728390376</v>
       </c>
       <c r="P74">
-        <v>-3.73897820736</v>
+        <v>-3.799433460239999</v>
       </c>
       <c r="Q74">
-        <v>-1.83897820736</v>
+        <v>-1.899433460239999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4040578717522446</v>
+        <v>0.4173266818171426</v>
       </c>
       <c r="T74">
-        <v>4.669301057318992</v>
+        <v>4.842238133515992</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04794455174562494</v>
+        <v>0.04728777706417802</v>
       </c>
       <c r="W74">
-        <v>0.2244946746983816</v>
+        <v>0.2246495421682669</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1410133874871321</v>
+        <v>0.1390816972475825</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7514,22 +7514,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2766723698734633</v>
+        <v>0.2785723698734633</v>
       </c>
       <c r="C75">
-        <v>-7.431947350758794</v>
+        <v>-7.940033670878723</v>
       </c>
       <c r="D75">
-        <v>14.6556326492412</v>
+        <v>14.53600632912127</v>
       </c>
       <c r="E75">
-        <v>28.31158</v>
+        <v>28.70004</v>
       </c>
       <c r="F75">
-        <v>28.35758</v>
+        <v>28.74604</v>
       </c>
       <c r="G75">
         <v>6.27</v>
@@ -7550,37 +7550,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M75">
-        <v>6.686717363999999</v>
+        <v>6.778316232</v>
       </c>
       <c r="N75">
-        <v>-5.756717363999998</v>
+        <v>-5.848316232</v>
       </c>
       <c r="O75">
-        <v>-1.95728390376</v>
+        <v>-1.98842751888</v>
       </c>
       <c r="P75">
-        <v>-3.799433460239999</v>
+        <v>-3.85988871312</v>
       </c>
       <c r="Q75">
-        <v>-1.899433460239999</v>
+        <v>-1.95988871312</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4173266818171426</v>
+        <v>0.4316161695793403</v>
       </c>
       <c r="T75">
-        <v>4.842238133515992</v>
+        <v>5.028478061728145</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04728777706417802</v>
+        <v>0.04664875304979724</v>
       </c>
       <c r="W75">
-        <v>0.2246495421682669</v>
+        <v>0.2248002240308578</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1390816972475825</v>
+        <v>0.1372022148523447</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7596,22 +7596,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2785723698734633</v>
+        <v>0.2804723698734634</v>
       </c>
       <c r="C76">
-        <v>-7.940033670878723</v>
+        <v>-8.446182907324513</v>
       </c>
       <c r="D76">
-        <v>14.53600632912127</v>
+        <v>14.41831709267548</v>
       </c>
       <c r="E76">
-        <v>28.70004</v>
+        <v>29.0885</v>
       </c>
       <c r="F76">
-        <v>28.74604</v>
+        <v>29.1345</v>
       </c>
       <c r="G76">
         <v>6.27</v>
@@ -7632,37 +7632,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M76">
-        <v>6.778316232</v>
+        <v>6.869915099999999</v>
       </c>
       <c r="N76">
-        <v>-5.848316232</v>
+        <v>-5.939915099999999</v>
       </c>
       <c r="O76">
-        <v>-1.98842751888</v>
+        <v>-2.019571134</v>
       </c>
       <c r="P76">
-        <v>-3.85988871312</v>
+        <v>-3.920343965999999</v>
       </c>
       <c r="Q76">
-        <v>-1.95988871312</v>
+        <v>-2.020343965999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4316161695793403</v>
+        <v>0.447048816362514</v>
       </c>
       <c r="T76">
-        <v>5.028478061728145</v>
+        <v>5.229617184197272</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04664875304979724</v>
+        <v>0.04602676967579994</v>
       </c>
       <c r="W76">
-        <v>0.2248002240308578</v>
+        <v>0.2249468877104464</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1372022148523447</v>
+        <v>0.1353728519876469</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7678,22 +7678,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2804723698734634</v>
+        <v>0.2823723698734633</v>
       </c>
       <c r="C77">
-        <v>-8.446182907324513</v>
+        <v>-8.950441732397515</v>
       </c>
       <c r="D77">
-        <v>14.41831709267548</v>
+        <v>14.30251826760248</v>
       </c>
       <c r="E77">
-        <v>29.0885</v>
+        <v>29.47696</v>
       </c>
       <c r="F77">
-        <v>29.1345</v>
+        <v>29.52296</v>
       </c>
       <c r="G77">
         <v>6.27</v>
@@ -7714,37 +7714,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M77">
-        <v>6.869915099999999</v>
+        <v>6.961513967999999</v>
       </c>
       <c r="N77">
-        <v>-5.939915099999999</v>
+        <v>-6.031513967999999</v>
       </c>
       <c r="O77">
-        <v>-2.019571134</v>
+        <v>-2.05071474912</v>
       </c>
       <c r="P77">
-        <v>-3.920343965999999</v>
+        <v>-3.980799218879999</v>
       </c>
       <c r="Q77">
-        <v>-2.020343965999999</v>
+        <v>-2.080799218879999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.447048816362514</v>
+        <v>0.4637675170442855</v>
       </c>
       <c r="T77">
-        <v>5.229617184197272</v>
+        <v>5.447517900205492</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04602676967579994</v>
+        <v>0.04542115428532889</v>
       </c>
       <c r="W77">
-        <v>0.2249468877104464</v>
+        <v>0.2250896918195195</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1353728519876469</v>
+        <v>0.1335916302509673</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7760,22 +7760,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2823723698734633</v>
+        <v>0.2842723698734633</v>
       </c>
       <c r="C78">
-        <v>-8.950441732397515</v>
+        <v>-9.452855330975261</v>
       </c>
       <c r="D78">
-        <v>14.30251826760248</v>
+        <v>14.18856466902474</v>
       </c>
       <c r="E78">
-        <v>29.47696</v>
+        <v>29.86542</v>
       </c>
       <c r="F78">
-        <v>29.52296</v>
+        <v>29.91142</v>
       </c>
       <c r="G78">
         <v>6.27</v>
@@ -7796,37 +7796,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M78">
-        <v>6.961513967999999</v>
+        <v>7.053112836</v>
       </c>
       <c r="N78">
-        <v>-6.031513967999999</v>
+        <v>-6.123112836000001</v>
       </c>
       <c r="O78">
-        <v>-2.05071474912</v>
+        <v>-2.08185836424</v>
       </c>
       <c r="P78">
-        <v>-3.980799218879999</v>
+        <v>-4.04125447176</v>
       </c>
       <c r="Q78">
-        <v>-2.080799218879999</v>
+        <v>-2.14125447176</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4637675170442855</v>
+        <v>0.4819400177853413</v>
       </c>
       <c r="T78">
-        <v>5.447517900205492</v>
+        <v>5.684366504562252</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04542115428532889</v>
+        <v>0.04483126916474019</v>
       </c>
       <c r="W78">
-        <v>0.2250896918195195</v>
+        <v>0.2252287867309543</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1335916302509673</v>
+        <v>0.1318566740139416</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7842,22 +7842,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2842723698734633</v>
+        <v>0.2861723698734633</v>
       </c>
       <c r="C79">
-        <v>-9.452855330975261</v>
+        <v>-9.953467459297407</v>
       </c>
       <c r="D79">
-        <v>14.18856466902474</v>
+        <v>14.07641254070259</v>
       </c>
       <c r="E79">
-        <v>29.86542</v>
+        <v>30.25388</v>
       </c>
       <c r="F79">
-        <v>29.91142</v>
+        <v>30.29988</v>
       </c>
       <c r="G79">
         <v>6.27</v>
@@ -7878,37 +7878,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M79">
-        <v>7.053112836</v>
+        <v>7.144711704</v>
       </c>
       <c r="N79">
-        <v>-6.123112836000001</v>
+        <v>-6.214711703999999</v>
       </c>
       <c r="O79">
-        <v>-2.08185836424</v>
+        <v>-2.11300197936</v>
       </c>
       <c r="P79">
-        <v>-4.04125447176</v>
+        <v>-4.101709724639999</v>
       </c>
       <c r="Q79">
-        <v>-2.14125447176</v>
+        <v>-2.201709724639999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4819400177853413</v>
+        <v>0.5017645640483115</v>
       </c>
       <c r="T79">
-        <v>5.684366504562252</v>
+        <v>5.942746800224174</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04483126916474019</v>
+        <v>0.04425650930365378</v>
       </c>
       <c r="W79">
-        <v>0.2252287867309543</v>
+        <v>0.2253643151061984</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1318566740139416</v>
+        <v>0.1301662038342759</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7924,22 +7924,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2861723698734633</v>
+        <v>0.2880723698734633</v>
       </c>
       <c r="C80">
-        <v>-9.953467459297407</v>
+        <v>-10.45232050098559</v>
       </c>
       <c r="D80">
-        <v>14.07641254070259</v>
+        <v>13.96601949901441</v>
       </c>
       <c r="E80">
-        <v>30.25388</v>
+        <v>30.64234</v>
       </c>
       <c r="F80">
-        <v>30.29988</v>
+        <v>30.68834</v>
       </c>
       <c r="G80">
         <v>6.27</v>
@@ -7960,37 +7960,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M80">
-        <v>7.144711704</v>
+        <v>7.236310572000001</v>
       </c>
       <c r="N80">
-        <v>-6.214711703999999</v>
+        <v>-6.306310572000001</v>
       </c>
       <c r="O80">
-        <v>-2.11300197936</v>
+        <v>-2.14414559448</v>
       </c>
       <c r="P80">
-        <v>-4.101709724639999</v>
+        <v>-4.162164977520001</v>
       </c>
       <c r="Q80">
-        <v>-2.201709724639999</v>
+        <v>-2.262164977520001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5017645640483115</v>
+        <v>0.5234771623363264</v>
       </c>
       <c r="T80">
-        <v>5.942746800224174</v>
+        <v>6.225734743091992</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04425650930365378</v>
+        <v>0.04369630032512652</v>
       </c>
       <c r="W80">
-        <v>0.2253643151061984</v>
+        <v>0.2254964123833352</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1301662038342759</v>
+        <v>0.1285185303680191</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8006,22 +8006,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2880723698734633</v>
+        <v>0.2899723698734633</v>
       </c>
       <c r="C81">
-        <v>-10.45232050098559</v>
+        <v>-10.94945552044778</v>
       </c>
       <c r="D81">
-        <v>13.96601949901441</v>
+        <v>13.85734447955222</v>
       </c>
       <c r="E81">
-        <v>30.64234</v>
+        <v>31.0308</v>
       </c>
       <c r="F81">
-        <v>30.68834</v>
+        <v>31.0768</v>
       </c>
       <c r="G81">
         <v>6.27</v>
@@ -8042,37 +8042,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M81">
-        <v>7.236310572000001</v>
+        <v>7.32790944</v>
       </c>
       <c r="N81">
-        <v>-6.306310572000001</v>
+        <v>-6.397909439999999</v>
       </c>
       <c r="O81">
-        <v>-2.14414559448</v>
+        <v>-2.1752892096</v>
       </c>
       <c r="P81">
-        <v>-4.162164977520001</v>
+        <v>-4.2226202304</v>
       </c>
       <c r="Q81">
-        <v>-2.262164977520001</v>
+        <v>-2.3226202304</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5234771623363264</v>
+        <v>0.5473610204531426</v>
       </c>
       <c r="T81">
-        <v>6.225734743091992</v>
+        <v>6.537021480246592</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04369630032512652</v>
+        <v>0.04315009657106244</v>
       </c>
       <c r="W81">
-        <v>0.2254964123833352</v>
+        <v>0.2256252072285435</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1285185303680191</v>
+        <v>0.126912048738419</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8088,22 +8088,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2899723698734633</v>
+        <v>0.2918723698734633</v>
       </c>
       <c r="C82">
-        <v>-10.94945552044778</v>
+        <v>-11.44491231380856</v>
       </c>
       <c r="D82">
-        <v>13.85734447955222</v>
+        <v>13.75034768619144</v>
       </c>
       <c r="E82">
-        <v>31.0308</v>
+        <v>31.41926</v>
       </c>
       <c r="F82">
-        <v>31.0768</v>
+        <v>31.46526</v>
       </c>
       <c r="G82">
         <v>6.27</v>
@@ -8124,37 +8124,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M82">
-        <v>7.32790944</v>
+        <v>7.419508308</v>
       </c>
       <c r="N82">
-        <v>-6.397909439999999</v>
+        <v>-6.489508308</v>
       </c>
       <c r="O82">
-        <v>-2.1752892096</v>
+        <v>-2.20643282472</v>
       </c>
       <c r="P82">
-        <v>-4.2226202304</v>
+        <v>-4.283075483279999</v>
       </c>
       <c r="Q82">
-        <v>-2.3226202304</v>
+        <v>-2.383075483279999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5473610204531426</v>
+        <v>0.5737589688980449</v>
       </c>
       <c r="T82">
-        <v>6.537021480246592</v>
+        <v>6.881075242364833</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04315009657106244</v>
+        <v>0.04261737932944439</v>
       </c>
       <c r="W82">
-        <v>0.2256252072285435</v>
+        <v>0.225750821954117</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.126912048738419</v>
+        <v>0.1253452333218953</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8170,22 +8170,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2918723698734633</v>
+        <v>0.2937723698734633</v>
       </c>
       <c r="C83">
-        <v>-11.44491231380856</v>
+        <v>-11.93872945749797</v>
       </c>
       <c r="D83">
-        <v>13.75034768619144</v>
+        <v>13.64499054250202</v>
       </c>
       <c r="E83">
-        <v>31.41926</v>
+        <v>31.80772</v>
       </c>
       <c r="F83">
-        <v>31.46526</v>
+        <v>31.85372</v>
       </c>
       <c r="G83">
         <v>6.27</v>
@@ -8206,37 +8206,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M83">
-        <v>7.419508308</v>
+        <v>7.511107176</v>
       </c>
       <c r="N83">
-        <v>-6.489508308</v>
+        <v>-6.581107176</v>
       </c>
       <c r="O83">
-        <v>-2.20643282472</v>
+        <v>-2.23757643984</v>
       </c>
       <c r="P83">
-        <v>-4.283075483279999</v>
+        <v>-4.34353073616</v>
       </c>
       <c r="Q83">
-        <v>-2.383075483279999</v>
+        <v>-2.44353073616</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5737589688980449</v>
+        <v>0.603090022725714</v>
       </c>
       <c r="T83">
-        <v>6.881075242364833</v>
+        <v>7.26335720027399</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04261737932944439</v>
+        <v>0.04209765519128043</v>
       </c>
       <c r="W83">
-        <v>0.225750821954117</v>
+        <v>0.2258733729058961</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1253452333218953</v>
+        <v>0.1238166329155307</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8252,22 +8252,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2937723698734633</v>
+        <v>0.2956723698734633</v>
       </c>
       <c r="C84">
-        <v>-11.93872945749797</v>
+        <v>-12.43094435462358</v>
       </c>
       <c r="D84">
-        <v>13.64499054250202</v>
+        <v>13.54123564537641</v>
       </c>
       <c r="E84">
-        <v>31.80772</v>
+        <v>32.19618</v>
       </c>
       <c r="F84">
-        <v>31.85372</v>
+        <v>32.24218</v>
       </c>
       <c r="G84">
         <v>6.27</v>
@@ -8288,37 +8288,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M84">
-        <v>7.511107176</v>
+        <v>7.602706044</v>
       </c>
       <c r="N84">
-        <v>-6.581107176</v>
+        <v>-6.672706044</v>
       </c>
       <c r="O84">
-        <v>-2.23757643984</v>
+        <v>-2.26872005496</v>
       </c>
       <c r="P84">
-        <v>-4.34353073616</v>
+        <v>-4.40398598904</v>
       </c>
       <c r="Q84">
-        <v>-2.44353073616</v>
+        <v>-2.50398598904</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.603090022725714</v>
+        <v>0.6358717887684031</v>
       </c>
       <c r="T84">
-        <v>7.26335720027399</v>
+        <v>7.690613506172461</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04209765519128043</v>
+        <v>0.04159045452632525</v>
       </c>
       <c r="W84">
-        <v>0.2258733729058961</v>
+        <v>0.2259929708226925</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1238166329155307</v>
+        <v>0.1223248662538977</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8334,22 +8334,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2956723698734633</v>
+        <v>0.2975723698734633</v>
       </c>
       <c r="C85">
-        <v>-12.43094435462358</v>
+        <v>-12.92159327924286</v>
       </c>
       <c r="D85">
-        <v>13.54123564537641</v>
+        <v>13.43904672075714</v>
       </c>
       <c r="E85">
-        <v>32.19618</v>
+        <v>32.58464</v>
       </c>
       <c r="F85">
-        <v>32.24218</v>
+        <v>32.63064</v>
       </c>
       <c r="G85">
         <v>6.27</v>
@@ -8370,37 +8370,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M85">
-        <v>7.602706044</v>
+        <v>7.694304912000001</v>
       </c>
       <c r="N85">
-        <v>-6.672706044</v>
+        <v>-6.764304912</v>
       </c>
       <c r="O85">
-        <v>-2.26872005496</v>
+        <v>-2.29986367008</v>
       </c>
       <c r="P85">
-        <v>-4.40398598904</v>
+        <v>-4.464441241919999</v>
       </c>
       <c r="Q85">
-        <v>-2.50398598904</v>
+        <v>-2.56444124192</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6358717887684031</v>
+        <v>0.6727512755664284</v>
       </c>
       <c r="T85">
-        <v>7.690613506172461</v>
+        <v>8.171276850308242</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04159045452632525</v>
+        <v>0.04109533006767851</v>
       </c>
       <c r="W85">
-        <v>0.2259929708226925</v>
+        <v>0.2261097211700414</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1223248662538977</v>
+        <v>0.1208686178461134</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8416,22 +8416,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2975723698734632</v>
+        <v>0.2994723698734633</v>
       </c>
       <c r="C86">
-        <v>-12.92159327924285</v>
+        <v>-13.41071141864596</v>
       </c>
       <c r="D86">
-        <v>13.43904672075714</v>
+        <v>13.33838858135404</v>
       </c>
       <c r="E86">
-        <v>32.58463999999999</v>
+        <v>32.9731</v>
       </c>
       <c r="F86">
-        <v>32.63063999999999</v>
+        <v>33.01909999999999</v>
       </c>
       <c r="G86">
         <v>6.27</v>
@@ -8452,37 +8452,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M86">
-        <v>7.694304911999999</v>
+        <v>7.785903779999999</v>
       </c>
       <c r="N86">
-        <v>-6.764304911999998</v>
+        <v>-6.855903779999998</v>
       </c>
       <c r="O86">
-        <v>-2.29986367008</v>
+        <v>-2.3310072852</v>
       </c>
       <c r="P86">
-        <v>-4.464441241919999</v>
+        <v>-4.524896494799998</v>
       </c>
       <c r="Q86">
-        <v>-2.564441241919999</v>
+        <v>-2.624896494799998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.672751275566428</v>
+        <v>0.7145480272708565</v>
       </c>
       <c r="T86">
-        <v>8.171276850308235</v>
+        <v>8.716028640328785</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04109533006767852</v>
+        <v>0.04061185559629406</v>
       </c>
       <c r="W86">
-        <v>0.2261097211700414</v>
+        <v>0.2262237244503938</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1208686178461134</v>
+        <v>0.1194466341067473</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8498,22 +8498,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2994723698734633</v>
+        <v>0.3013723698734633</v>
       </c>
       <c r="C87">
-        <v>-13.41071141864596</v>
+        <v>-13.89833291375249</v>
       </c>
       <c r="D87">
-        <v>13.33838858135404</v>
+        <v>13.2392270862475</v>
       </c>
       <c r="E87">
-        <v>32.9731</v>
+        <v>33.36156</v>
       </c>
       <c r="F87">
-        <v>33.01909999999999</v>
+        <v>33.40756</v>
       </c>
       <c r="G87">
         <v>6.27</v>
@@ -8534,37 +8534,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M87">
-        <v>7.785903779999999</v>
+        <v>7.877502647999999</v>
       </c>
       <c r="N87">
-        <v>-6.855903779999998</v>
+        <v>-6.947502647999999</v>
       </c>
       <c r="O87">
-        <v>-2.3310072852</v>
+        <v>-2.36215090032</v>
       </c>
       <c r="P87">
-        <v>-4.524896494799998</v>
+        <v>-4.585351747679999</v>
       </c>
       <c r="Q87">
-        <v>-2.624896494799998</v>
+        <v>-2.685351747679999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7145480272708565</v>
+        <v>0.7623157435044892</v>
       </c>
       <c r="T87">
-        <v>8.716028640328785</v>
+        <v>9.338602114637984</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04061185559629406</v>
+        <v>0.04013962471726739</v>
       </c>
       <c r="W87">
-        <v>0.2262237244503938</v>
+        <v>0.2263350764916684</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1194466341067473</v>
+        <v>0.1180577197566688</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8580,22 +8580,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3013723698734633</v>
+        <v>0.3032723698734633</v>
       </c>
       <c r="C88">
-        <v>-13.89833291375249</v>
+        <v>-14.3844908977196</v>
       </c>
       <c r="D88">
-        <v>13.2392270862475</v>
+        <v>13.1415291022804</v>
       </c>
       <c r="E88">
-        <v>33.36156</v>
+        <v>33.75002</v>
       </c>
       <c r="F88">
-        <v>33.40756</v>
+        <v>33.79602</v>
       </c>
       <c r="G88">
         <v>6.27</v>
@@ -8616,37 +8616,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M88">
-        <v>7.877502647999999</v>
+        <v>7.969101516</v>
       </c>
       <c r="N88">
-        <v>-6.947502647999999</v>
+        <v>-7.039101516000001</v>
       </c>
       <c r="O88">
-        <v>-2.36215090032</v>
+        <v>-2.39329451544</v>
       </c>
       <c r="P88">
-        <v>-4.585351747679999</v>
+        <v>-4.64580700056</v>
       </c>
       <c r="Q88">
-        <v>-2.685351747679999</v>
+        <v>-2.74580700056</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7623157435044892</v>
+        <v>0.8174323391586806</v>
       </c>
       <c r="T88">
-        <v>9.338602114637984</v>
+        <v>10.05695612345629</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04013962471726739</v>
+        <v>0.03967824972051718</v>
       </c>
       <c r="W88">
-        <v>0.2263350764916684</v>
+        <v>0.2264438687159021</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1180577197566688</v>
+        <v>0.1167007344721093</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8662,22 +8662,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3032723698734633</v>
+        <v>0.3051723698734633</v>
       </c>
       <c r="C89">
-        <v>-14.3844908977196</v>
+        <v>-14.86921753285316</v>
       </c>
       <c r="D89">
-        <v>13.1415291022804</v>
+        <v>13.04526246714685</v>
       </c>
       <c r="E89">
-        <v>33.75002</v>
+        <v>34.13848</v>
       </c>
       <c r="F89">
-        <v>33.79602</v>
+        <v>34.18448</v>
       </c>
       <c r="G89">
         <v>6.27</v>
@@ -8698,37 +8698,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M89">
-        <v>7.969101516</v>
+        <v>8.060700384</v>
       </c>
       <c r="N89">
-        <v>-7.039101516000001</v>
+        <v>-7.130700384000001</v>
       </c>
       <c r="O89">
-        <v>-2.39329451544</v>
+        <v>-2.42443813056</v>
       </c>
       <c r="P89">
-        <v>-4.64580700056</v>
+        <v>-4.70626225344</v>
       </c>
       <c r="Q89">
-        <v>-2.74580700056</v>
+        <v>-2.80626225344</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8174323391586806</v>
+        <v>0.8817350340885709</v>
       </c>
       <c r="T89">
-        <v>10.05695612345629</v>
+        <v>10.89503580041098</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03967824972051718</v>
+        <v>0.03922736051914767</v>
       </c>
       <c r="W89">
-        <v>0.2264438687159021</v>
+        <v>0.226550188389585</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1167007344721093</v>
+        <v>0.1153745897621989</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8744,22 +8744,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3051723698734633</v>
+        <v>0.3070723698734633</v>
       </c>
       <c r="C90">
-        <v>-14.86921753285316</v>
+        <v>-15.3525440459084</v>
       </c>
       <c r="D90">
-        <v>13.04526246714685</v>
+        <v>12.95039595409159</v>
       </c>
       <c r="E90">
-        <v>34.13848</v>
+        <v>34.52694</v>
       </c>
       <c r="F90">
-        <v>34.18448</v>
+        <v>34.57294</v>
       </c>
       <c r="G90">
         <v>6.27</v>
@@ -8780,37 +8780,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M90">
-        <v>8.060700384</v>
+        <v>8.152299251999999</v>
       </c>
       <c r="N90">
-        <v>-7.130700384000001</v>
+        <v>-7.222299251999999</v>
       </c>
       <c r="O90">
-        <v>-2.42443813056</v>
+        <v>-2.45558174568</v>
       </c>
       <c r="P90">
-        <v>-4.70626225344</v>
+        <v>-4.766717506319999</v>
       </c>
       <c r="Q90">
-        <v>-2.80626225344</v>
+        <v>-2.866717506319999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8817350340885709</v>
+        <v>0.9577291280966228</v>
       </c>
       <c r="T90">
-        <v>10.89503580041098</v>
+        <v>11.88549360044835</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03922736051914767</v>
+        <v>0.03878660365938198</v>
       </c>
       <c r="W90">
-        <v>0.226550188389585</v>
+        <v>0.2266541188571177</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1153745897621989</v>
+        <v>0.1140782460570058</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8826,22 +8826,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3070723698734633</v>
+        <v>0.3089723698734633</v>
       </c>
       <c r="C91">
-        <v>-15.3525440459084</v>
+        <v>-15.83450076186155</v>
       </c>
       <c r="D91">
-        <v>12.95039595409159</v>
+        <v>12.85689923813845</v>
       </c>
       <c r="E91">
-        <v>34.52694</v>
+        <v>34.9154</v>
       </c>
       <c r="F91">
-        <v>34.57294</v>
+        <v>34.9614</v>
       </c>
       <c r="G91">
         <v>6.27</v>
@@ -8862,37 +8862,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M91">
-        <v>8.152299251999999</v>
+        <v>8.243898119999999</v>
       </c>
       <c r="N91">
-        <v>-7.222299251999999</v>
+        <v>-7.313898119999999</v>
       </c>
       <c r="O91">
-        <v>-2.45558174568</v>
+        <v>-2.4867253608</v>
       </c>
       <c r="P91">
-        <v>-4.766717506319999</v>
+        <v>-4.8271727592</v>
       </c>
       <c r="Q91">
-        <v>-2.866717506319999</v>
+        <v>-2.9271727592</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9577291280966228</v>
+        <v>1.048922040906285</v>
       </c>
       <c r="T91">
-        <v>11.88549360044835</v>
+        <v>13.07404296049318</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03878660365938198</v>
+        <v>0.03835564139649995</v>
       </c>
       <c r="W91">
-        <v>0.2266541188571177</v>
+        <v>0.2267557397587053</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1140782460570058</v>
+        <v>0.1128107099897057</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8908,22 +8908,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3089723698734633</v>
+        <v>0.3108723698734633</v>
       </c>
       <c r="C92">
-        <v>-15.83450076186155</v>
+        <v>-16.31511713622876</v>
       </c>
       <c r="D92">
-        <v>12.85689923813845</v>
+        <v>12.76474286377124</v>
       </c>
       <c r="E92">
-        <v>34.9154</v>
+        <v>35.30386</v>
       </c>
       <c r="F92">
-        <v>34.9614</v>
+        <v>35.34986</v>
       </c>
       <c r="G92">
         <v>6.27</v>
@@ -8944,37 +8944,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M92">
-        <v>8.243898119999999</v>
+        <v>8.335496988000001</v>
       </c>
       <c r="N92">
-        <v>-7.313898119999999</v>
+        <v>-7.405496988000001</v>
       </c>
       <c r="O92">
-        <v>-2.4867253608</v>
+        <v>-2.517868975920001</v>
       </c>
       <c r="P92">
-        <v>-4.8271727592</v>
+        <v>-4.88762801208</v>
       </c>
       <c r="Q92">
-        <v>-2.9271727592</v>
+        <v>-2.987628012080001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.048922040906285</v>
+        <v>1.160380045451428</v>
       </c>
       <c r="T92">
-        <v>13.07404296049318</v>
+        <v>14.52671440054798</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03835564139649995</v>
+        <v>0.03793415083170324</v>
       </c>
       <c r="W92">
-        <v>0.2267557397587053</v>
+        <v>0.2268551272338844</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1128107099897057</v>
+        <v>0.1115710318579506</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8990,22 +8990,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3108723698734633</v>
+        <v>0.3127723698734634</v>
       </c>
       <c r="C93">
-        <v>-16.31511713622876</v>
+        <v>-16.7944217860053</v>
       </c>
       <c r="D93">
-        <v>12.76474286377124</v>
+        <v>12.6738982139947</v>
       </c>
       <c r="E93">
-        <v>35.30386</v>
+        <v>35.69232</v>
       </c>
       <c r="F93">
-        <v>35.34986</v>
+        <v>35.73832</v>
       </c>
       <c r="G93">
         <v>6.27</v>
@@ -9026,37 +9026,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M93">
-        <v>8.335496988000001</v>
+        <v>8.427095856000001</v>
       </c>
       <c r="N93">
-        <v>-7.405496988000001</v>
+        <v>-7.497095856000001</v>
       </c>
       <c r="O93">
-        <v>-2.517868975920001</v>
+        <v>-2.549012591040001</v>
       </c>
       <c r="P93">
-        <v>-4.88762801208</v>
+        <v>-4.948083264960001</v>
       </c>
       <c r="Q93">
-        <v>-2.987628012080001</v>
+        <v>-3.048083264960001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.160380045451428</v>
+        <v>1.299702551132857</v>
       </c>
       <c r="T93">
-        <v>14.52671440054798</v>
+        <v>16.34255370061648</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03793415083170324</v>
+        <v>0.03752182310527168</v>
       </c>
       <c r="W93">
-        <v>0.2268551272338844</v>
+        <v>0.226952354111777</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1115710318579506</v>
+        <v>0.110358303250799</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9072,22 +9072,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3127723698734634</v>
+        <v>0.3146723698734633</v>
       </c>
       <c r="C94">
-        <v>-16.7944217860053</v>
+        <v>-17.2724425192927</v>
       </c>
       <c r="D94">
-        <v>12.6738982139947</v>
+        <v>12.5843374807073</v>
       </c>
       <c r="E94">
-        <v>35.69232</v>
+        <v>36.08078</v>
       </c>
       <c r="F94">
-        <v>35.73832</v>
+        <v>36.12678</v>
       </c>
       <c r="G94">
         <v>6.27</v>
@@ -9108,37 +9108,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M94">
-        <v>8.427095856000001</v>
+        <v>8.518694723999999</v>
       </c>
       <c r="N94">
-        <v>-7.497095856000001</v>
+        <v>-7.588694724</v>
       </c>
       <c r="O94">
-        <v>-2.549012591040001</v>
+        <v>-2.58015620616</v>
       </c>
       <c r="P94">
-        <v>-4.948083264960001</v>
+        <v>-5.00853851784</v>
       </c>
       <c r="Q94">
-        <v>-3.048083264960001</v>
+        <v>-3.10853851784</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.299702551132857</v>
+        <v>1.47883148700898</v>
       </c>
       <c r="T94">
-        <v>16.34255370061648</v>
+        <v>18.67720422927598</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03752182310527168</v>
+        <v>0.03711836264177414</v>
       </c>
       <c r="W94">
-        <v>0.226952354111777</v>
+        <v>0.2270474900890697</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.110358303250799</v>
+        <v>0.1091716548287475</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9154,22 +9154,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3146723698734633</v>
+        <v>0.3165723698734633</v>
       </c>
       <c r="C95">
-        <v>-17.2724425192927</v>
+        <v>-17.74920636367874</v>
       </c>
       <c r="D95">
-        <v>12.5843374807073</v>
+        <v>12.49603363632126</v>
       </c>
       <c r="E95">
-        <v>36.08078</v>
+        <v>36.46924</v>
       </c>
       <c r="F95">
-        <v>36.12678</v>
+        <v>36.51524</v>
       </c>
       <c r="G95">
         <v>6.27</v>
@@ -9190,37 +9190,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M95">
-        <v>8.518694723999999</v>
+        <v>8.610293592</v>
       </c>
       <c r="N95">
-        <v>-7.588694724</v>
+        <v>-7.680293592</v>
       </c>
       <c r="O95">
-        <v>-2.58015620616</v>
+        <v>-2.61129982128</v>
       </c>
       <c r="P95">
-        <v>-5.00853851784</v>
+        <v>-5.06899377072</v>
       </c>
       <c r="Q95">
-        <v>-3.10853851784</v>
+        <v>-3.16899377072</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.47883148700898</v>
+        <v>1.717670068177144</v>
       </c>
       <c r="T95">
-        <v>18.67720422927598</v>
+        <v>21.79007160082199</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03711836264177414</v>
+        <v>0.0367234864434574</v>
       </c>
       <c r="W95">
-        <v>0.2270474900890697</v>
+        <v>0.2271406018966328</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1091716548287475</v>
+        <v>0.1080102542454628</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9236,22 +9236,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3165723698734633</v>
+        <v>0.3184723698734633</v>
       </c>
       <c r="C96">
-        <v>-17.74920636367874</v>
+        <v>-18.22473959343072</v>
       </c>
       <c r="D96">
-        <v>12.49603363632126</v>
+        <v>12.40896040656928</v>
       </c>
       <c r="E96">
-        <v>36.46924</v>
+        <v>36.8577</v>
       </c>
       <c r="F96">
-        <v>36.51524</v>
+        <v>36.9037</v>
       </c>
       <c r="G96">
         <v>6.27</v>
@@ -9272,37 +9272,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M96">
-        <v>8.610293592</v>
+        <v>8.70189246</v>
       </c>
       <c r="N96">
-        <v>-7.680293592</v>
+        <v>-7.77189246</v>
       </c>
       <c r="O96">
-        <v>-2.61129982128</v>
+        <v>-2.6424434364</v>
       </c>
       <c r="P96">
-        <v>-5.06899377072</v>
+        <v>-5.129449023599999</v>
       </c>
       <c r="Q96">
-        <v>-3.16899377072</v>
+        <v>-3.2294490236</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.717670068177144</v>
+        <v>2.052044081812573</v>
       </c>
       <c r="T96">
-        <v>21.79007160082199</v>
+        <v>26.1480859209864</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0367234864434574</v>
+        <v>0.03633692342826311</v>
       </c>
       <c r="W96">
-        <v>0.2271406018966328</v>
+        <v>0.2272317534556156</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1080102542454628</v>
+        <v>0.1068733042007738</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9318,22 +9318,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3184723698734633</v>
+        <v>0.3203723698734633</v>
       </c>
       <c r="C97">
-        <v>-18.22473959343072</v>
+        <v>-18.69906775555988</v>
       </c>
       <c r="D97">
-        <v>12.40896040656928</v>
+        <v>12.32309224444012</v>
       </c>
       <c r="E97">
-        <v>36.8577</v>
+        <v>37.24616</v>
       </c>
       <c r="F97">
-        <v>36.9037</v>
+        <v>37.29216</v>
       </c>
       <c r="G97">
         <v>6.27</v>
@@ -9354,37 +9354,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M97">
-        <v>8.70189246</v>
+        <v>8.793491328000002</v>
       </c>
       <c r="N97">
-        <v>-7.77189246</v>
+        <v>-7.863491328000002</v>
       </c>
       <c r="O97">
-        <v>-2.6424434364</v>
+        <v>-2.673587051520001</v>
       </c>
       <c r="P97">
-        <v>-5.129449023599999</v>
+        <v>-5.189904276480001</v>
       </c>
       <c r="Q97">
-        <v>-3.2294490236</v>
+        <v>-3.289904276480001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.052044081812573</v>
+        <v>2.553605102265717</v>
       </c>
       <c r="T97">
-        <v>26.1480859209864</v>
+        <v>32.685107401233</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03633692342826311</v>
+        <v>0.03595841380921869</v>
       </c>
       <c r="W97">
-        <v>0.2272317534556156</v>
+        <v>0.2273210060237862</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1068733042007738</v>
+        <v>0.105760040615349</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9400,22 +9400,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3203723698734633</v>
+        <v>0.3222723698734633</v>
       </c>
       <c r="C98">
-        <v>-18.69906775555987</v>
+        <v>-19.17221569481092</v>
       </c>
       <c r="D98">
-        <v>12.32309224444012</v>
+        <v>12.23840430518908</v>
       </c>
       <c r="E98">
-        <v>37.24616</v>
+        <v>37.63462</v>
       </c>
       <c r="F98">
-        <v>37.29216</v>
+        <v>37.68062</v>
       </c>
       <c r="G98">
         <v>6.27</v>
@@ -9436,37 +9436,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M98">
-        <v>8.793491328</v>
+        <v>8.885090196</v>
       </c>
       <c r="N98">
-        <v>-7.863491328</v>
+        <v>-7.955090196</v>
       </c>
       <c r="O98">
-        <v>-2.67358705152</v>
+        <v>-2.70473066664</v>
       </c>
       <c r="P98">
-        <v>-5.18990427648</v>
+        <v>-5.250359529360001</v>
       </c>
       <c r="Q98">
-        <v>-3.28990427648</v>
+        <v>-3.350359529360001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.55360510226571</v>
+        <v>3.389540136354281</v>
       </c>
       <c r="T98">
-        <v>32.68510740123292</v>
+        <v>43.5801432016439</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0359584138092187</v>
+        <v>0.03558770851221645</v>
       </c>
       <c r="W98">
-        <v>0.2273210060237862</v>
+        <v>0.2274084183328194</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.105760040615349</v>
+        <v>0.1046697309182836</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9482,22 +9482,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3222723698734633</v>
+        <v>0.3241723698734633</v>
       </c>
       <c r="C99">
-        <v>-19.17221569481092</v>
+        <v>-19.64420757762827</v>
       </c>
       <c r="D99">
-        <v>12.23840430518908</v>
+        <v>12.15487242237172</v>
       </c>
       <c r="E99">
-        <v>37.63462</v>
+        <v>38.02307999999999</v>
       </c>
       <c r="F99">
-        <v>37.68062</v>
+        <v>38.06907999999999</v>
       </c>
       <c r="G99">
         <v>6.27</v>
@@ -9518,37 +9518,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M99">
-        <v>8.885090196</v>
+        <v>8.976689063999999</v>
       </c>
       <c r="N99">
-        <v>-7.955090196</v>
+        <v>-8.046689063999999</v>
       </c>
       <c r="O99">
-        <v>-2.70473066664</v>
+        <v>-2.73587428176</v>
       </c>
       <c r="P99">
-        <v>-5.250359529360001</v>
+        <v>-5.31081478224</v>
       </c>
       <c r="Q99">
-        <v>-3.350359529360001</v>
+        <v>-3.41081478224</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.389540136354281</v>
+        <v>5.061410204531421</v>
       </c>
       <c r="T99">
-        <v>43.5801432016439</v>
+        <v>65.37021480246584</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03558770851221645</v>
+        <v>0.03522456862943873</v>
       </c>
       <c r="W99">
-        <v>0.2274084183328194</v>
+        <v>0.2274940467171784</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1046697309182836</v>
+        <v>0.1036016724395257</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9564,22 +9564,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3241723698734633</v>
+        <v>0.3260723698734633</v>
       </c>
       <c r="C100">
-        <v>-19.64420757762827</v>
+        <v>-20.11506691514746</v>
       </c>
       <c r="D100">
-        <v>12.15487242237172</v>
+        <v>12.07247308485254</v>
       </c>
       <c r="E100">
-        <v>38.02307999999999</v>
+        <v>38.41154</v>
       </c>
       <c r="F100">
-        <v>38.06907999999999</v>
+        <v>38.45753999999999</v>
       </c>
       <c r="G100">
         <v>6.27</v>
@@ -9600,37 +9600,37 @@
         <v>0.9300000000000002</v>
       </c>
       <c r="M100">
-        <v>8.976689063999999</v>
+        <v>9.068287931999999</v>
       </c>
       <c r="N100">
-        <v>-8.046689063999999</v>
+        <v>-8.138287931999999</v>
       </c>
       <c r="O100">
-        <v>-2.73587428176</v>
+        <v>-2.76701789688</v>
       </c>
       <c r="P100">
-        <v>-5.31081478224</v>
+        <v>-5.371270035119999</v>
       </c>
       <c r="Q100">
-        <v>-3.41081478224</v>
+        <v>-3.471270035119999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.061410204531421</v>
+        <v>10.07702040906284</v>
       </c>
       <c r="T100">
-        <v>65.37021480246584</v>
+        <v>130.7404296049317</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03522456862943873</v>
+        <v>0.03486876490590905</v>
       </c>
       <c r="W100">
-        <v>0.2274940467171784</v>
+        <v>0.2275779452351867</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9638,91 +9638,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1036016724395257</v>
+        <v>0.1025551908997324</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3260723698734633</v>
-      </c>
-      <c r="C101">
-        <v>-20.11506691514746</v>
-      </c>
-      <c r="D101">
-        <v>12.07247308485254</v>
-      </c>
-      <c r="E101">
-        <v>38.41154</v>
-      </c>
-      <c r="F101">
-        <v>38.45753999999999</v>
-      </c>
-      <c r="G101">
-        <v>6.27</v>
-      </c>
-      <c r="H101">
-        <v>38.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.83</v>
-      </c>
-      <c r="K101">
-        <v>1.9</v>
-      </c>
-      <c r="L101">
-        <v>0.9300000000000002</v>
-      </c>
-      <c r="M101">
-        <v>9.068287931999999</v>
-      </c>
-      <c r="N101">
-        <v>-8.138287931999999</v>
-      </c>
-      <c r="O101">
-        <v>-2.76701789688</v>
-      </c>
-      <c r="P101">
-        <v>-5.371270035119999</v>
-      </c>
-      <c r="Q101">
-        <v>-3.471270035119999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.07702040906284</v>
-      </c>
-      <c r="T101">
-        <v>130.7404296049317</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03486876490590905</v>
-      </c>
-      <c r="W101">
-        <v>0.2275779452351867</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1025551908997324</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
